--- a/PDS.xlsx
+++ b/PDS.xlsx
@@ -3459,6 +3459,100 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -3471,57 +3565,422 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="25" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="25" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3531,12 +3990,6 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3553,20 +4006,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -3626,10 +4065,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3645,468 +4080,165 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="33" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4114,152 +4246,35 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4273,13 +4288,83 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4290,33 +4375,6 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -4333,6 +4391,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4344,6 +4405,18 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -4374,68 +4447,55 @@
     <xf numFmtId="49" fontId="6" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4447,14 +4507,79 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4462,12 +4587,276 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -4485,36 +4874,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -4524,394 +4905,13 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -10063,20 +10063,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="375"/>
-      <c r="B1" s="376"/>
-      <c r="C1" s="376"/>
-      <c r="D1" s="376"/>
-      <c r="E1" s="376"/>
-      <c r="F1" s="376"/>
-      <c r="G1" s="376"/>
-      <c r="H1" s="376"/>
-      <c r="I1" s="376"/>
-      <c r="J1" s="376"/>
-      <c r="K1" s="376"/>
-      <c r="L1" s="376"/>
-      <c r="M1" s="376"/>
-      <c r="N1" s="377"/>
+      <c r="A1" s="346"/>
+      <c r="B1" s="347"/>
+      <c r="C1" s="347"/>
+      <c r="D1" s="347"/>
+      <c r="E1" s="347"/>
+      <c r="F1" s="347"/>
+      <c r="G1" s="347"/>
+      <c r="H1" s="347"/>
+      <c r="I1" s="347"/>
+      <c r="J1" s="347"/>
+      <c r="K1" s="347"/>
+      <c r="L1" s="347"/>
+      <c r="M1" s="347"/>
+      <c r="N1" s="348"/>
     </row>
     <row r="2" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="138"/>
@@ -10106,58 +10106,58 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="378" t="s">
+      <c r="A3" s="349" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="379"/>
-      <c r="C3" s="379"/>
-      <c r="D3" s="379"/>
-      <c r="E3" s="379"/>
-      <c r="F3" s="379"/>
-      <c r="G3" s="379"/>
-      <c r="H3" s="379"/>
-      <c r="I3" s="379"/>
-      <c r="J3" s="379"/>
-      <c r="K3" s="379"/>
-      <c r="L3" s="379"/>
-      <c r="M3" s="379"/>
-      <c r="N3" s="380"/>
+      <c r="B3" s="350"/>
+      <c r="C3" s="350"/>
+      <c r="D3" s="350"/>
+      <c r="E3" s="350"/>
+      <c r="F3" s="350"/>
+      <c r="G3" s="350"/>
+      <c r="H3" s="350"/>
+      <c r="I3" s="350"/>
+      <c r="J3" s="350"/>
+      <c r="K3" s="350"/>
+      <c r="L3" s="350"/>
+      <c r="M3" s="350"/>
+      <c r="N3" s="351"/>
     </row>
     <row r="4" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="411" t="s">
+      <c r="A4" s="382" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="412"/>
-      <c r="C4" s="412"/>
-      <c r="D4" s="412"/>
-      <c r="E4" s="412"/>
-      <c r="F4" s="412"/>
-      <c r="G4" s="412"/>
-      <c r="H4" s="412"/>
-      <c r="I4" s="412"/>
-      <c r="J4" s="412"/>
-      <c r="K4" s="412"/>
-      <c r="L4" s="412"/>
-      <c r="M4" s="412"/>
-      <c r="N4" s="413"/>
+      <c r="B4" s="383"/>
+      <c r="C4" s="383"/>
+      <c r="D4" s="383"/>
+      <c r="E4" s="383"/>
+      <c r="F4" s="383"/>
+      <c r="G4" s="383"/>
+      <c r="H4" s="383"/>
+      <c r="I4" s="383"/>
+      <c r="J4" s="383"/>
+      <c r="K4" s="383"/>
+      <c r="L4" s="383"/>
+      <c r="M4" s="383"/>
+      <c r="N4" s="384"/>
     </row>
     <row r="5" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="285" t="s">
+      <c r="A5" s="430" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="286"/>
-      <c r="C5" s="286"/>
-      <c r="D5" s="286"/>
-      <c r="E5" s="286"/>
-      <c r="F5" s="286"/>
-      <c r="G5" s="286"/>
-      <c r="H5" s="286"/>
-      <c r="I5" s="286"/>
-      <c r="J5" s="286"/>
-      <c r="K5" s="286"/>
-      <c r="L5" s="286"/>
-      <c r="M5" s="286"/>
-      <c r="N5" s="287"/>
+      <c r="B5" s="431"/>
+      <c r="C5" s="431"/>
+      <c r="D5" s="431"/>
+      <c r="E5" s="431"/>
+      <c r="F5" s="431"/>
+      <c r="G5" s="431"/>
+      <c r="H5" s="431"/>
+      <c r="I5" s="431"/>
+      <c r="J5" s="431"/>
+      <c r="K5" s="431"/>
+      <c r="L5" s="431"/>
+      <c r="M5" s="431"/>
+      <c r="N5" s="432"/>
     </row>
     <row r="6" spans="1:18" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A6" s="170"/>
@@ -10194,42 +10194,42 @@
       <c r="N8" s="134"/>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="381" t="s">
+      <c r="A9" s="352" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="382"/>
-      <c r="C9" s="382"/>
-      <c r="D9" s="382"/>
-      <c r="E9" s="382"/>
-      <c r="F9" s="382"/>
-      <c r="G9" s="382"/>
-      <c r="H9" s="382"/>
-      <c r="I9" s="382"/>
-      <c r="J9" s="382"/>
-      <c r="K9" s="382"/>
-      <c r="L9" s="382"/>
-      <c r="M9" s="382"/>
-      <c r="N9" s="383"/>
+      <c r="B9" s="353"/>
+      <c r="C9" s="353"/>
+      <c r="D9" s="353"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
+      <c r="G9" s="353"/>
+      <c r="H9" s="353"/>
+      <c r="I9" s="353"/>
+      <c r="J9" s="353"/>
+      <c r="K9" s="353"/>
+      <c r="L9" s="353"/>
+      <c r="M9" s="353"/>
+      <c r="N9" s="354"/>
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="399" t="s">
+      <c r="B10" s="372" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="325"/>
-      <c r="D10" s="392"/>
-      <c r="E10" s="392"/>
-      <c r="F10" s="392"/>
-      <c r="G10" s="392"/>
-      <c r="H10" s="392"/>
-      <c r="I10" s="392"/>
-      <c r="J10" s="392"/>
-      <c r="K10" s="392"/>
-      <c r="L10" s="392"/>
-      <c r="M10" s="392"/>
-      <c r="N10" s="393"/>
+      <c r="C10" s="373"/>
+      <c r="D10" s="363"/>
+      <c r="E10" s="363"/>
+      <c r="F10" s="363"/>
+      <c r="G10" s="363"/>
+      <c r="H10" s="363"/>
+      <c r="I10" s="363"/>
+      <c r="J10" s="363"/>
+      <c r="K10" s="363"/>
+      <c r="L10" s="363"/>
+      <c r="M10" s="363"/>
+      <c r="N10" s="364"/>
       <c r="P10" s="69" t="s">
         <v>11</v>
       </c>
@@ -10238,10 +10238,10 @@
       <c r="A11" s="143" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="400" t="s">
+      <c r="B11" s="374" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="401"/>
+      <c r="C11" s="375"/>
       <c r="D11" s="178"/>
       <c r="E11" s="179"/>
       <c r="F11" s="179"/>
@@ -10250,11 +10250,11 @@
       <c r="I11" s="179"/>
       <c r="J11" s="179"/>
       <c r="K11" s="179"/>
-      <c r="L11" s="326" t="s">
+      <c r="L11" s="400" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="327"/>
-      <c r="N11" s="328"/>
+      <c r="M11" s="401"/>
+      <c r="N11" s="402"/>
       <c r="P11" s="70" t="s">
         <v>15</v>
       </c>
@@ -10264,10 +10264,10 @@
     </row>
     <row r="12" spans="1:18" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="144"/>
-      <c r="B12" s="402" t="s">
+      <c r="B12" s="376" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="403"/>
+      <c r="C12" s="377"/>
       <c r="D12" s="175"/>
       <c r="E12" s="176"/>
       <c r="F12" s="176"/>
@@ -10290,23 +10290,23 @@
       <c r="A13" s="211" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="324" t="s">
+      <c r="B13" s="462" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="325"/>
-      <c r="D13" s="329"/>
-      <c r="E13" s="329"/>
-      <c r="F13" s="330"/>
+      <c r="C13" s="373"/>
+      <c r="D13" s="403"/>
+      <c r="E13" s="403"/>
+      <c r="F13" s="404"/>
       <c r="G13" s="76" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="121"/>
       <c r="I13" s="121"/>
-      <c r="J13" s="336"/>
-      <c r="K13" s="337"/>
-      <c r="L13" s="337"/>
-      <c r="M13" s="337"/>
-      <c r="N13" s="338"/>
+      <c r="J13" s="410"/>
+      <c r="K13" s="411"/>
+      <c r="L13" s="411"/>
+      <c r="M13" s="411"/>
+      <c r="N13" s="412"/>
       <c r="P13" s="70" t="s">
         <v>23</v>
       </c>
@@ -10340,21 +10340,21 @@
         <v>26</v>
       </c>
       <c r="C15" s="71"/>
-      <c r="D15" s="353"/>
-      <c r="E15" s="353"/>
-      <c r="F15" s="354"/>
-      <c r="G15" s="334" t="s">
+      <c r="D15" s="425"/>
+      <c r="E15" s="425"/>
+      <c r="F15" s="426"/>
+      <c r="G15" s="408" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="335"/>
-      <c r="I15" s="335"/>
+      <c r="H15" s="409"/>
+      <c r="I15" s="409"/>
       <c r="J15" s="122"/>
       <c r="K15" s="123"/>
-      <c r="L15" s="339" t="s">
+      <c r="L15" s="413" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="339"/>
-      <c r="N15" s="340"/>
+      <c r="M15" s="413"/>
+      <c r="N15" s="414"/>
       <c r="P15" s="70" t="s">
         <v>29</v>
       </c>
@@ -10370,14 +10370,14 @@
         <v>32</v>
       </c>
       <c r="C16" s="72"/>
-      <c r="D16" s="394"/>
-      <c r="E16" s="394"/>
-      <c r="F16" s="395"/>
-      <c r="G16" s="331" t="s">
+      <c r="D16" s="365"/>
+      <c r="E16" s="365"/>
+      <c r="F16" s="366"/>
+      <c r="G16" s="405" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="332"/>
-      <c r="I16" s="333"/>
+      <c r="H16" s="406"/>
+      <c r="I16" s="407"/>
       <c r="N16" s="134"/>
       <c r="P16" s="70" t="s">
         <v>34</v>
@@ -10387,49 +10387,49 @@
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="307">
+      <c r="A17" s="446">
         <v>6</v>
       </c>
-      <c r="B17" s="320" t="s">
+      <c r="B17" s="458" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="321"/>
-      <c r="D17" s="318"/>
-      <c r="E17" s="318"/>
-      <c r="F17" s="318"/>
+      <c r="C17" s="459"/>
+      <c r="D17" s="457"/>
+      <c r="E17" s="457"/>
+      <c r="F17" s="457"/>
       <c r="G17" s="77" t="s">
         <v>37</v>
       </c>
       <c r="H17" s="78"/>
-      <c r="I17" s="349"/>
-      <c r="J17" s="341"/>
-      <c r="K17" s="341"/>
-      <c r="L17" s="341"/>
-      <c r="M17" s="341"/>
-      <c r="N17" s="342"/>
+      <c r="I17" s="328"/>
+      <c r="J17" s="329"/>
+      <c r="K17" s="329"/>
+      <c r="L17" s="329"/>
+      <c r="M17" s="329"/>
+      <c r="N17" s="330"/>
       <c r="Q17" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="308"/>
-      <c r="B18" s="322"/>
-      <c r="C18" s="323"/>
-      <c r="D18" s="319"/>
-      <c r="E18" s="319"/>
-      <c r="F18" s="319"/>
+      <c r="A18" s="447"/>
+      <c r="B18" s="460"/>
+      <c r="C18" s="461"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
       <c r="G18" s="130"/>
       <c r="H18" s="79"/>
-      <c r="I18" s="344" t="s">
+      <c r="I18" s="415" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="288"/>
-      <c r="K18" s="288"/>
-      <c r="L18" s="288" t="s">
+      <c r="J18" s="416"/>
+      <c r="K18" s="416"/>
+      <c r="L18" s="416" t="s">
         <v>40</v>
       </c>
-      <c r="M18" s="288"/>
-      <c r="N18" s="289"/>
+      <c r="M18" s="416"/>
+      <c r="N18" s="417"/>
       <c r="Q18" s="3" t="s">
         <v>41</v>
       </c>
@@ -10443,100 +10443,100 @@
       <c r="F19" s="135"/>
       <c r="G19" s="130"/>
       <c r="H19" s="79"/>
-      <c r="I19" s="290"/>
-      <c r="J19" s="291"/>
-      <c r="K19" s="291"/>
-      <c r="L19" s="294"/>
-      <c r="M19" s="291"/>
-      <c r="N19" s="295"/>
+      <c r="I19" s="433"/>
+      <c r="J19" s="434"/>
+      <c r="K19" s="434"/>
+      <c r="L19" s="437"/>
+      <c r="M19" s="434"/>
+      <c r="N19" s="438"/>
       <c r="Q19" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="308"/>
+      <c r="A20" s="447"/>
       <c r="B20" s="194"/>
       <c r="C20" s="113"/>
       <c r="D20" s="114"/>
-      <c r="E20" s="319"/>
-      <c r="F20" s="319"/>
+      <c r="E20" s="370"/>
+      <c r="F20" s="370"/>
       <c r="G20" s="128"/>
       <c r="H20" s="133"/>
-      <c r="I20" s="292"/>
-      <c r="J20" s="293"/>
-      <c r="K20" s="293"/>
-      <c r="L20" s="293"/>
-      <c r="M20" s="293"/>
-      <c r="N20" s="296"/>
+      <c r="I20" s="435"/>
+      <c r="J20" s="436"/>
+      <c r="K20" s="436"/>
+      <c r="L20" s="436"/>
+      <c r="M20" s="436"/>
+      <c r="N20" s="439"/>
       <c r="Q20" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="309"/>
+      <c r="A21" s="448"/>
       <c r="B21" s="195"/>
       <c r="C21" s="111"/>
       <c r="D21" s="115"/>
-      <c r="E21" s="398"/>
-      <c r="F21" s="398"/>
+      <c r="E21" s="371"/>
+      <c r="F21" s="371"/>
       <c r="G21" s="128"/>
       <c r="H21" s="133"/>
-      <c r="I21" s="297" t="s">
+      <c r="I21" s="440" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="298"/>
-      <c r="K21" s="298"/>
-      <c r="L21" s="434" t="s">
+      <c r="J21" s="441"/>
+      <c r="K21" s="441"/>
+      <c r="L21" s="325" t="s">
         <v>45</v>
       </c>
-      <c r="M21" s="435"/>
-      <c r="N21" s="436"/>
+      <c r="M21" s="326"/>
+      <c r="N21" s="327"/>
       <c r="Q21" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="316" t="s">
+      <c r="A22" s="455" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="283" t="s">
+      <c r="B22" s="389" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="284"/>
-      <c r="D22" s="363"/>
-      <c r="E22" s="363"/>
-      <c r="F22" s="363"/>
+      <c r="C22" s="390"/>
+      <c r="D22" s="385"/>
+      <c r="E22" s="385"/>
+      <c r="F22" s="385"/>
       <c r="G22" s="128"/>
       <c r="H22" s="133"/>
-      <c r="I22" s="349"/>
-      <c r="J22" s="341"/>
-      <c r="K22" s="341"/>
-      <c r="L22" s="341"/>
-      <c r="M22" s="341"/>
-      <c r="N22" s="342"/>
+      <c r="I22" s="328"/>
+      <c r="J22" s="329"/>
+      <c r="K22" s="329"/>
+      <c r="L22" s="329"/>
+      <c r="M22" s="329"/>
+      <c r="N22" s="330"/>
       <c r="Q22" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="317"/>
-      <c r="B23" s="364"/>
-      <c r="C23" s="365"/>
-      <c r="D23" s="302"/>
-      <c r="E23" s="302"/>
-      <c r="F23" s="302"/>
+      <c r="A23" s="456"/>
+      <c r="B23" s="391"/>
+      <c r="C23" s="392"/>
+      <c r="D23" s="386"/>
+      <c r="E23" s="386"/>
+      <c r="F23" s="386"/>
       <c r="G23" s="128"/>
       <c r="H23" s="133"/>
-      <c r="I23" s="439" t="s">
+      <c r="I23" s="333" t="s">
         <v>50</v>
       </c>
-      <c r="J23" s="440"/>
-      <c r="K23" s="440"/>
-      <c r="L23" s="437" t="s">
+      <c r="J23" s="334"/>
+      <c r="K23" s="334"/>
+      <c r="L23" s="331" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="437"/>
-      <c r="N23" s="438"/>
+      <c r="M23" s="331"/>
+      <c r="N23" s="332"/>
       <c r="Q23" s="3" t="s">
         <v>52</v>
       </c>
@@ -10545,163 +10545,163 @@
       <c r="A24" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="366" t="s">
+      <c r="B24" s="379" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="367"/>
-      <c r="D24" s="343"/>
-      <c r="E24" s="343"/>
-      <c r="F24" s="343"/>
-      <c r="G24" s="404" t="s">
+      <c r="C24" s="380"/>
+      <c r="D24" s="381"/>
+      <c r="E24" s="381"/>
+      <c r="F24" s="381"/>
+      <c r="G24" s="339" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="405"/>
-      <c r="I24" s="350"/>
-      <c r="J24" s="351"/>
-      <c r="K24" s="351"/>
-      <c r="L24" s="351"/>
-      <c r="M24" s="351"/>
-      <c r="N24" s="352"/>
+      <c r="H24" s="318"/>
+      <c r="I24" s="422"/>
+      <c r="J24" s="423"/>
+      <c r="K24" s="423"/>
+      <c r="L24" s="423"/>
+      <c r="M24" s="423"/>
+      <c r="N24" s="424"/>
       <c r="Q24" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="299" t="s">
+      <c r="A25" s="387" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="283" t="s">
+      <c r="B25" s="389" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="284"/>
-      <c r="D25" s="301"/>
-      <c r="E25" s="301"/>
-      <c r="F25" s="301"/>
+      <c r="C25" s="390"/>
+      <c r="D25" s="369"/>
+      <c r="E25" s="369"/>
+      <c r="F25" s="369"/>
       <c r="G25" s="84" t="s">
         <v>59</v>
       </c>
       <c r="H25" s="73"/>
-      <c r="I25" s="355"/>
-      <c r="J25" s="356"/>
-      <c r="K25" s="356"/>
-      <c r="L25" s="356"/>
-      <c r="M25" s="356"/>
-      <c r="N25" s="443"/>
+      <c r="I25" s="343"/>
+      <c r="J25" s="337"/>
+      <c r="K25" s="337"/>
+      <c r="L25" s="337"/>
+      <c r="M25" s="337"/>
+      <c r="N25" s="338"/>
       <c r="Q25" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="300"/>
-      <c r="B26" s="364"/>
-      <c r="C26" s="365"/>
-      <c r="D26" s="302"/>
-      <c r="E26" s="302"/>
-      <c r="F26" s="302"/>
+      <c r="A26" s="388"/>
+      <c r="B26" s="391"/>
+      <c r="C26" s="392"/>
+      <c r="D26" s="386"/>
+      <c r="E26" s="386"/>
+      <c r="F26" s="386"/>
       <c r="G26" s="128"/>
       <c r="H26" s="133"/>
-      <c r="I26" s="344" t="s">
+      <c r="I26" s="415" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="288"/>
-      <c r="K26" s="288"/>
-      <c r="L26" s="288" t="s">
+      <c r="J26" s="416"/>
+      <c r="K26" s="416"/>
+      <c r="L26" s="416" t="s">
         <v>40</v>
       </c>
-      <c r="M26" s="288"/>
-      <c r="N26" s="289"/>
+      <c r="M26" s="416"/>
+      <c r="N26" s="417"/>
       <c r="Q26" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="299" t="s">
+      <c r="A27" s="387" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="368" t="s">
+      <c r="B27" s="393" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="284"/>
-      <c r="D27" s="301"/>
-      <c r="E27" s="301"/>
-      <c r="F27" s="301"/>
+      <c r="C27" s="390"/>
+      <c r="D27" s="369"/>
+      <c r="E27" s="369"/>
+      <c r="F27" s="369"/>
       <c r="G27" s="130"/>
       <c r="H27" s="79"/>
-      <c r="I27" s="355"/>
-      <c r="J27" s="356"/>
-      <c r="K27" s="356"/>
-      <c r="L27" s="356"/>
-      <c r="M27" s="356"/>
-      <c r="N27" s="443"/>
+      <c r="I27" s="343"/>
+      <c r="J27" s="337"/>
+      <c r="K27" s="337"/>
+      <c r="L27" s="337"/>
+      <c r="M27" s="337"/>
+      <c r="N27" s="338"/>
       <c r="Q27" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="300"/>
-      <c r="B28" s="364"/>
-      <c r="C28" s="365"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
-      <c r="F28" s="302"/>
+      <c r="A28" s="388"/>
+      <c r="B28" s="391"/>
+      <c r="C28" s="392"/>
+      <c r="D28" s="386"/>
+      <c r="E28" s="386"/>
+      <c r="F28" s="386"/>
       <c r="G28" s="130"/>
       <c r="H28" s="79"/>
-      <c r="I28" s="345" t="s">
+      <c r="I28" s="418" t="s">
         <v>44</v>
       </c>
-      <c r="J28" s="346"/>
-      <c r="K28" s="346"/>
-      <c r="L28" s="347" t="s">
+      <c r="J28" s="419"/>
+      <c r="K28" s="419"/>
+      <c r="L28" s="420" t="s">
         <v>45</v>
       </c>
-      <c r="M28" s="346"/>
-      <c r="N28" s="348"/>
+      <c r="M28" s="419"/>
+      <c r="N28" s="421"/>
       <c r="Q28" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="299" t="s">
+      <c r="A29" s="387" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="283" t="s">
+      <c r="B29" s="389" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="284"/>
-      <c r="D29" s="303"/>
-      <c r="E29" s="301"/>
-      <c r="F29" s="304"/>
+      <c r="C29" s="390"/>
+      <c r="D29" s="442"/>
+      <c r="E29" s="369"/>
+      <c r="F29" s="443"/>
       <c r="G29" s="130"/>
       <c r="H29" s="137"/>
-      <c r="I29" s="372"/>
-      <c r="J29" s="373"/>
-      <c r="K29" s="373"/>
-      <c r="L29" s="373"/>
-      <c r="M29" s="373"/>
-      <c r="N29" s="374"/>
+      <c r="I29" s="397"/>
+      <c r="J29" s="398"/>
+      <c r="K29" s="398"/>
+      <c r="L29" s="398"/>
+      <c r="M29" s="398"/>
+      <c r="N29" s="399"/>
       <c r="Q29" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="300"/>
-      <c r="B30" s="364"/>
-      <c r="C30" s="365"/>
-      <c r="D30" s="305"/>
-      <c r="E30" s="302"/>
-      <c r="F30" s="306"/>
+      <c r="A30" s="388"/>
+      <c r="B30" s="391"/>
+      <c r="C30" s="392"/>
+      <c r="D30" s="444"/>
+      <c r="E30" s="386"/>
+      <c r="F30" s="445"/>
       <c r="G30" s="130"/>
       <c r="H30" s="137"/>
-      <c r="I30" s="441" t="s">
+      <c r="I30" s="335" t="s">
         <v>50</v>
       </c>
-      <c r="J30" s="441"/>
-      <c r="K30" s="441"/>
-      <c r="L30" s="441" t="s">
+      <c r="J30" s="335"/>
+      <c r="K30" s="335"/>
+      <c r="L30" s="335" t="s">
         <v>51</v>
       </c>
-      <c r="M30" s="441"/>
-      <c r="N30" s="442"/>
+      <c r="M30" s="335"/>
+      <c r="N30" s="336"/>
       <c r="Q30" s="3" t="s">
         <v>69</v>
       </c>
@@ -10714,19 +10714,19 @@
         <v>71</v>
       </c>
       <c r="C31" s="72"/>
-      <c r="D31" s="301"/>
-      <c r="E31" s="301"/>
-      <c r="F31" s="301"/>
-      <c r="G31" s="404" t="s">
+      <c r="D31" s="369"/>
+      <c r="E31" s="369"/>
+      <c r="F31" s="369"/>
+      <c r="G31" s="339" t="s">
         <v>55</v>
       </c>
-      <c r="H31" s="405"/>
-      <c r="I31" s="369"/>
-      <c r="J31" s="370"/>
-      <c r="K31" s="370"/>
-      <c r="L31" s="370"/>
-      <c r="M31" s="370"/>
-      <c r="N31" s="371"/>
+      <c r="H31" s="318"/>
+      <c r="I31" s="394"/>
+      <c r="J31" s="395"/>
+      <c r="K31" s="395"/>
+      <c r="L31" s="395"/>
+      <c r="M31" s="395"/>
+      <c r="N31" s="396"/>
       <c r="Q31" s="3" t="s">
         <v>72</v>
       </c>
@@ -10739,42 +10739,42 @@
         <v>74</v>
       </c>
       <c r="C32" s="72"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="D32" s="381"/>
+      <c r="E32" s="381"/>
+      <c r="F32" s="381"/>
       <c r="G32" s="127" t="s">
         <v>75</v>
       </c>
       <c r="H32" s="131"/>
-      <c r="I32" s="357"/>
-      <c r="J32" s="358"/>
-      <c r="K32" s="358"/>
-      <c r="L32" s="358"/>
-      <c r="M32" s="358"/>
-      <c r="N32" s="359"/>
+      <c r="I32" s="340"/>
+      <c r="J32" s="341"/>
+      <c r="K32" s="341"/>
+      <c r="L32" s="341"/>
+      <c r="M32" s="341"/>
+      <c r="N32" s="342"/>
       <c r="Q32" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="407" t="s">
+      <c r="A33" s="378" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="366"/>
-      <c r="C33" s="367"/>
-      <c r="D33" s="343"/>
-      <c r="E33" s="343"/>
-      <c r="F33" s="343"/>
+      <c r="B33" s="379"/>
+      <c r="C33" s="380"/>
+      <c r="D33" s="381"/>
+      <c r="E33" s="381"/>
+      <c r="F33" s="381"/>
       <c r="G33" s="177" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="129"/>
-      <c r="I33" s="357"/>
-      <c r="J33" s="358"/>
-      <c r="K33" s="358"/>
-      <c r="L33" s="358"/>
-      <c r="M33" s="358"/>
-      <c r="N33" s="359"/>
+      <c r="I33" s="340"/>
+      <c r="J33" s="341"/>
+      <c r="K33" s="341"/>
+      <c r="L33" s="341"/>
+      <c r="M33" s="341"/>
+      <c r="N33" s="342"/>
       <c r="Q33" s="3" t="s">
         <v>79</v>
       </c>
@@ -10785,19 +10785,19 @@
       </c>
       <c r="B34" s="196"/>
       <c r="C34" s="132"/>
-      <c r="D34" s="301"/>
-      <c r="E34" s="301"/>
-      <c r="F34" s="301"/>
+      <c r="D34" s="369"/>
+      <c r="E34" s="369"/>
+      <c r="F34" s="369"/>
       <c r="G34" s="84" t="s">
         <v>81</v>
       </c>
       <c r="H34" s="73"/>
-      <c r="I34" s="360"/>
-      <c r="J34" s="361"/>
-      <c r="K34" s="361"/>
-      <c r="L34" s="361"/>
-      <c r="M34" s="361"/>
-      <c r="N34" s="362"/>
+      <c r="I34" s="427"/>
+      <c r="J34" s="428"/>
+      <c r="K34" s="428"/>
+      <c r="L34" s="428"/>
+      <c r="M34" s="428"/>
+      <c r="N34" s="429"/>
       <c r="Q34" s="3" t="s">
         <v>82</v>
       </c>
@@ -10831,21 +10831,21 @@
         <v>86</v>
       </c>
       <c r="C36" s="200"/>
-      <c r="D36" s="310"/>
-      <c r="E36" s="311"/>
-      <c r="F36" s="311"/>
-      <c r="G36" s="311"/>
-      <c r="H36" s="312"/>
-      <c r="I36" s="444" t="s">
+      <c r="D36" s="449"/>
+      <c r="E36" s="450"/>
+      <c r="F36" s="450"/>
+      <c r="G36" s="450"/>
+      <c r="H36" s="451"/>
+      <c r="I36" s="344" t="s">
         <v>87</v>
       </c>
-      <c r="J36" s="444"/>
-      <c r="K36" s="444"/>
-      <c r="L36" s="445"/>
-      <c r="M36" s="386" t="s">
+      <c r="J36" s="344"/>
+      <c r="K36" s="344"/>
+      <c r="L36" s="345"/>
+      <c r="M36" s="357" t="s">
         <v>88</v>
       </c>
-      <c r="N36" s="387"/>
+      <c r="N36" s="358"/>
       <c r="Q36" s="3" t="s">
         <v>89</v>
       </c>
@@ -10856,19 +10856,19 @@
         <v>90</v>
       </c>
       <c r="C37" s="137"/>
-      <c r="D37" s="408"/>
-      <c r="E37" s="409"/>
-      <c r="F37" s="410"/>
-      <c r="G37" s="406" t="s">
+      <c r="D37" s="284"/>
+      <c r="E37" s="285"/>
+      <c r="F37" s="286"/>
+      <c r="G37" s="300" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="406"/>
-      <c r="I37" s="270"/>
-      <c r="J37" s="270"/>
-      <c r="K37" s="270"/>
-      <c r="L37" s="271"/>
-      <c r="M37" s="277"/>
-      <c r="N37" s="278"/>
+      <c r="H37" s="300"/>
+      <c r="I37" s="282"/>
+      <c r="J37" s="282"/>
+      <c r="K37" s="282"/>
+      <c r="L37" s="283"/>
+      <c r="M37" s="280"/>
+      <c r="N37" s="281"/>
       <c r="Q37" s="3" t="s">
         <v>92</v>
       </c>
@@ -10879,17 +10879,17 @@
         <v>93</v>
       </c>
       <c r="C38" s="191"/>
-      <c r="D38" s="408"/>
-      <c r="E38" s="409"/>
-      <c r="F38" s="409"/>
-      <c r="G38" s="409"/>
-      <c r="H38" s="410"/>
-      <c r="I38" s="270"/>
-      <c r="J38" s="270"/>
-      <c r="K38" s="270"/>
-      <c r="L38" s="271"/>
-      <c r="M38" s="277"/>
-      <c r="N38" s="278"/>
+      <c r="D38" s="284"/>
+      <c r="E38" s="285"/>
+      <c r="F38" s="285"/>
+      <c r="G38" s="285"/>
+      <c r="H38" s="286"/>
+      <c r="I38" s="282"/>
+      <c r="J38" s="282"/>
+      <c r="K38" s="282"/>
+      <c r="L38" s="283"/>
+      <c r="M38" s="280"/>
+      <c r="N38" s="281"/>
       <c r="Q38" s="3" t="s">
         <v>94</v>
       </c>
@@ -10900,17 +10900,17 @@
         <v>95</v>
       </c>
       <c r="C39" s="72"/>
-      <c r="D39" s="313"/>
-      <c r="E39" s="314"/>
-      <c r="F39" s="314"/>
-      <c r="G39" s="314"/>
-      <c r="H39" s="315"/>
-      <c r="I39" s="270"/>
-      <c r="J39" s="270"/>
-      <c r="K39" s="270"/>
-      <c r="L39" s="271"/>
-      <c r="M39" s="277"/>
-      <c r="N39" s="278"/>
+      <c r="D39" s="452"/>
+      <c r="E39" s="453"/>
+      <c r="F39" s="453"/>
+      <c r="G39" s="453"/>
+      <c r="H39" s="454"/>
+      <c r="I39" s="282"/>
+      <c r="J39" s="282"/>
+      <c r="K39" s="282"/>
+      <c r="L39" s="283"/>
+      <c r="M39" s="280"/>
+      <c r="N39" s="281"/>
       <c r="Q39" s="3" t="s">
         <v>96</v>
       </c>
@@ -10921,17 +10921,17 @@
         <v>97</v>
       </c>
       <c r="C40" s="72"/>
-      <c r="D40" s="313"/>
-      <c r="E40" s="314"/>
-      <c r="F40" s="314"/>
-      <c r="G40" s="314"/>
-      <c r="H40" s="315"/>
-      <c r="I40" s="270"/>
-      <c r="J40" s="270"/>
-      <c r="K40" s="270"/>
-      <c r="L40" s="271"/>
-      <c r="M40" s="277"/>
-      <c r="N40" s="278"/>
+      <c r="D40" s="452"/>
+      <c r="E40" s="453"/>
+      <c r="F40" s="453"/>
+      <c r="G40" s="453"/>
+      <c r="H40" s="454"/>
+      <c r="I40" s="282"/>
+      <c r="J40" s="282"/>
+      <c r="K40" s="282"/>
+      <c r="L40" s="283"/>
+      <c r="M40" s="280"/>
+      <c r="N40" s="281"/>
       <c r="Q40" s="3" t="s">
         <v>98</v>
       </c>
@@ -10942,17 +10942,17 @@
         <v>99</v>
       </c>
       <c r="C41" s="72"/>
-      <c r="D41" s="313"/>
-      <c r="E41" s="314"/>
-      <c r="F41" s="314"/>
-      <c r="G41" s="314"/>
-      <c r="H41" s="315"/>
-      <c r="I41" s="270"/>
-      <c r="J41" s="270"/>
-      <c r="K41" s="270"/>
-      <c r="L41" s="271"/>
-      <c r="M41" s="277"/>
-      <c r="N41" s="278"/>
+      <c r="D41" s="452"/>
+      <c r="E41" s="453"/>
+      <c r="F41" s="453"/>
+      <c r="G41" s="453"/>
+      <c r="H41" s="454"/>
+      <c r="I41" s="282"/>
+      <c r="J41" s="282"/>
+      <c r="K41" s="282"/>
+      <c r="L41" s="283"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="281"/>
       <c r="Q41" s="3" t="s">
         <v>100</v>
       </c>
@@ -10963,17 +10963,17 @@
         <v>101</v>
       </c>
       <c r="C42" s="112"/>
-      <c r="D42" s="313"/>
-      <c r="E42" s="314"/>
-      <c r="F42" s="314"/>
-      <c r="G42" s="314"/>
-      <c r="H42" s="315"/>
-      <c r="I42" s="270"/>
-      <c r="J42" s="270"/>
-      <c r="K42" s="270"/>
-      <c r="L42" s="271"/>
-      <c r="M42" s="277"/>
-      <c r="N42" s="278"/>
+      <c r="D42" s="452"/>
+      <c r="E42" s="453"/>
+      <c r="F42" s="453"/>
+      <c r="G42" s="453"/>
+      <c r="H42" s="454"/>
+      <c r="I42" s="282"/>
+      <c r="J42" s="282"/>
+      <c r="K42" s="282"/>
+      <c r="L42" s="283"/>
+      <c r="M42" s="280"/>
+      <c r="N42" s="281"/>
       <c r="Q42" s="3" t="s">
         <v>102</v>
       </c>
@@ -10986,17 +10986,17 @@
         <v>104</v>
       </c>
       <c r="C43" s="78"/>
-      <c r="D43" s="408"/>
-      <c r="E43" s="409"/>
-      <c r="F43" s="409"/>
-      <c r="G43" s="409"/>
-      <c r="H43" s="410"/>
-      <c r="I43" s="270"/>
-      <c r="J43" s="270"/>
-      <c r="K43" s="270"/>
-      <c r="L43" s="271"/>
-      <c r="M43" s="277"/>
-      <c r="N43" s="278"/>
+      <c r="D43" s="284"/>
+      <c r="E43" s="285"/>
+      <c r="F43" s="285"/>
+      <c r="G43" s="285"/>
+      <c r="H43" s="286"/>
+      <c r="I43" s="282"/>
+      <c r="J43" s="282"/>
+      <c r="K43" s="282"/>
+      <c r="L43" s="283"/>
+      <c r="M43" s="280"/>
+      <c r="N43" s="281"/>
       <c r="Q43" s="3" t="s">
         <v>105</v>
       </c>
@@ -11007,19 +11007,19 @@
         <v>13</v>
       </c>
       <c r="C44" s="133"/>
-      <c r="D44" s="408"/>
-      <c r="E44" s="409"/>
-      <c r="F44" s="410"/>
-      <c r="G44" s="406" t="s">
+      <c r="D44" s="284"/>
+      <c r="E44" s="285"/>
+      <c r="F44" s="286"/>
+      <c r="G44" s="300" t="s">
         <v>106</v>
       </c>
-      <c r="H44" s="406"/>
-      <c r="I44" s="270"/>
-      <c r="J44" s="270"/>
-      <c r="K44" s="270"/>
-      <c r="L44" s="271"/>
-      <c r="M44" s="277"/>
-      <c r="N44" s="278"/>
+      <c r="H44" s="300"/>
+      <c r="I44" s="282"/>
+      <c r="J44" s="282"/>
+      <c r="K44" s="282"/>
+      <c r="L44" s="283"/>
+      <c r="M44" s="280"/>
+      <c r="N44" s="281"/>
       <c r="Q44" s="3" t="s">
         <v>107</v>
       </c>
@@ -11030,17 +11030,17 @@
         <v>17</v>
       </c>
       <c r="C45" s="184"/>
-      <c r="D45" s="408"/>
-      <c r="E45" s="409"/>
-      <c r="F45" s="409"/>
-      <c r="G45" s="409"/>
-      <c r="H45" s="410"/>
-      <c r="I45" s="270"/>
-      <c r="J45" s="270"/>
-      <c r="K45" s="270"/>
-      <c r="L45" s="271"/>
-      <c r="M45" s="277"/>
-      <c r="N45" s="278"/>
+      <c r="D45" s="284"/>
+      <c r="E45" s="285"/>
+      <c r="F45" s="285"/>
+      <c r="G45" s="285"/>
+      <c r="H45" s="286"/>
+      <c r="I45" s="282"/>
+      <c r="J45" s="282"/>
+      <c r="K45" s="282"/>
+      <c r="L45" s="283"/>
+      <c r="M45" s="280"/>
+      <c r="N45" s="281"/>
       <c r="Q45" s="3" t="s">
         <v>108</v>
       </c>
@@ -11049,21 +11049,21 @@
       <c r="A46" s="128" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="283" t="s">
+      <c r="B46" s="389" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="283"/>
-      <c r="D46" s="283"/>
-      <c r="E46" s="283"/>
-      <c r="F46" s="283"/>
-      <c r="G46" s="283"/>
-      <c r="H46" s="284"/>
-      <c r="I46" s="270"/>
-      <c r="J46" s="270"/>
-      <c r="K46" s="270"/>
-      <c r="L46" s="271"/>
-      <c r="M46" s="277"/>
-      <c r="N46" s="278"/>
+      <c r="C46" s="389"/>
+      <c r="D46" s="389"/>
+      <c r="E46" s="389"/>
+      <c r="F46" s="389"/>
+      <c r="G46" s="389"/>
+      <c r="H46" s="390"/>
+      <c r="I46" s="282"/>
+      <c r="J46" s="282"/>
+      <c r="K46" s="282"/>
+      <c r="L46" s="283"/>
+      <c r="M46" s="280"/>
+      <c r="N46" s="281"/>
       <c r="Q46" s="3" t="s">
         <v>111</v>
       </c>
@@ -11074,17 +11074,17 @@
         <v>10</v>
       </c>
       <c r="C47" s="133"/>
-      <c r="D47" s="463"/>
-      <c r="E47" s="464"/>
-      <c r="F47" s="464"/>
-      <c r="G47" s="464"/>
-      <c r="H47" s="465"/>
-      <c r="I47" s="270"/>
-      <c r="J47" s="270"/>
-      <c r="K47" s="270"/>
-      <c r="L47" s="271"/>
-      <c r="M47" s="277"/>
-      <c r="N47" s="278"/>
+      <c r="D47" s="297"/>
+      <c r="E47" s="298"/>
+      <c r="F47" s="298"/>
+      <c r="G47" s="298"/>
+      <c r="H47" s="299"/>
+      <c r="I47" s="282"/>
+      <c r="J47" s="282"/>
+      <c r="K47" s="282"/>
+      <c r="L47" s="283"/>
+      <c r="M47" s="280"/>
+      <c r="N47" s="281"/>
       <c r="Q47" s="3" t="s">
         <v>112</v>
       </c>
@@ -11095,17 +11095,17 @@
         <v>13</v>
       </c>
       <c r="C48" s="133"/>
-      <c r="D48" s="463"/>
-      <c r="E48" s="464"/>
-      <c r="F48" s="464"/>
-      <c r="G48" s="464"/>
-      <c r="H48" s="465"/>
-      <c r="I48" s="270"/>
-      <c r="J48" s="270"/>
-      <c r="K48" s="270"/>
-      <c r="L48" s="271"/>
-      <c r="M48" s="277"/>
-      <c r="N48" s="278"/>
+      <c r="D48" s="297"/>
+      <c r="E48" s="298"/>
+      <c r="F48" s="298"/>
+      <c r="G48" s="298"/>
+      <c r="H48" s="299"/>
+      <c r="I48" s="282"/>
+      <c r="J48" s="282"/>
+      <c r="K48" s="282"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="280"/>
+      <c r="N48" s="281"/>
       <c r="Q48" s="3" t="s">
         <v>113</v>
       </c>
@@ -11116,19 +11116,19 @@
         <v>17</v>
       </c>
       <c r="C49" s="186"/>
-      <c r="D49" s="274"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="275"/>
-      <c r="G49" s="275"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="272" t="s">
+      <c r="D49" s="465"/>
+      <c r="E49" s="466"/>
+      <c r="F49" s="466"/>
+      <c r="G49" s="466"/>
+      <c r="H49" s="467"/>
+      <c r="I49" s="463" t="s">
         <v>114</v>
       </c>
-      <c r="J49" s="272"/>
-      <c r="K49" s="272"/>
-      <c r="L49" s="272"/>
-      <c r="M49" s="272"/>
-      <c r="N49" s="273"/>
+      <c r="J49" s="463"/>
+      <c r="K49" s="463"/>
+      <c r="L49" s="463"/>
+      <c r="M49" s="463"/>
+      <c r="N49" s="464"/>
       <c r="Q49" s="3" t="s">
         <v>115</v>
       </c>
@@ -11144,47 +11144,47 @@
       <c r="F50" s="75"/>
       <c r="G50" s="75"/>
       <c r="H50" s="75"/>
-      <c r="I50" s="396" t="s">
+      <c r="I50" s="367" t="s">
         <v>117</v>
       </c>
-      <c r="J50" s="396"/>
-      <c r="K50" s="396"/>
-      <c r="L50" s="396"/>
-      <c r="M50" s="396"/>
-      <c r="N50" s="397"/>
+      <c r="J50" s="367"/>
+      <c r="K50" s="367"/>
+      <c r="L50" s="367"/>
+      <c r="M50" s="367"/>
+      <c r="N50" s="368"/>
       <c r="Q50" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="388" t="s">
+      <c r="A51" s="359" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="417" t="s">
+      <c r="B51" s="313" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="417"/>
-      <c r="D51" s="420" t="s">
+      <c r="C51" s="313"/>
+      <c r="D51" s="301" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="421"/>
-      <c r="F51" s="422"/>
-      <c r="G51" s="420" t="s">
+      <c r="E51" s="302"/>
+      <c r="F51" s="316"/>
+      <c r="G51" s="301" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="421"/>
-      <c r="I51" s="466"/>
-      <c r="J51" s="279" t="s">
+      <c r="H51" s="302"/>
+      <c r="I51" s="303"/>
+      <c r="J51" s="468" t="s">
         <v>123</v>
       </c>
-      <c r="K51" s="280"/>
-      <c r="L51" s="461" t="s">
+      <c r="K51" s="469"/>
+      <c r="L51" s="292" t="s">
         <v>124</v>
       </c>
-      <c r="M51" s="390" t="s">
+      <c r="M51" s="361" t="s">
         <v>125</v>
       </c>
-      <c r="N51" s="384" t="s">
+      <c r="N51" s="355" t="s">
         <v>126</v>
       </c>
       <c r="Q51" s="3" t="s">
@@ -11192,43 +11192,43 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="389"/>
-      <c r="B52" s="418"/>
-      <c r="C52" s="418"/>
-      <c r="D52" s="423"/>
-      <c r="E52" s="424"/>
-      <c r="F52" s="425"/>
-      <c r="G52" s="423"/>
-      <c r="H52" s="424"/>
-      <c r="I52" s="467"/>
-      <c r="J52" s="281"/>
-      <c r="K52" s="282"/>
-      <c r="L52" s="461"/>
-      <c r="M52" s="390"/>
-      <c r="N52" s="384"/>
+      <c r="A52" s="360"/>
+      <c r="B52" s="314"/>
+      <c r="C52" s="314"/>
+      <c r="D52" s="304"/>
+      <c r="E52" s="305"/>
+      <c r="F52" s="317"/>
+      <c r="G52" s="304"/>
+      <c r="H52" s="305"/>
+      <c r="I52" s="306"/>
+      <c r="J52" s="470"/>
+      <c r="K52" s="471"/>
+      <c r="L52" s="292"/>
+      <c r="M52" s="361"/>
+      <c r="N52" s="355"/>
       <c r="Q52" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
-      <c r="B53" s="419"/>
-      <c r="C53" s="419"/>
-      <c r="D53" s="426"/>
-      <c r="E53" s="427"/>
-      <c r="F53" s="405"/>
-      <c r="G53" s="426"/>
-      <c r="H53" s="427"/>
-      <c r="I53" s="468"/>
+      <c r="B53" s="315"/>
+      <c r="C53" s="315"/>
+      <c r="D53" s="307"/>
+      <c r="E53" s="308"/>
+      <c r="F53" s="318"/>
+      <c r="G53" s="307"/>
+      <c r="H53" s="308"/>
+      <c r="I53" s="309"/>
       <c r="J53" s="80" t="s">
         <v>129</v>
       </c>
       <c r="K53" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="L53" s="462"/>
-      <c r="M53" s="391"/>
-      <c r="N53" s="385"/>
+      <c r="L53" s="293"/>
+      <c r="M53" s="362"/>
+      <c r="N53" s="356"/>
       <c r="O53" s="82"/>
       <c r="P53" s="82"/>
       <c r="Q53" s="3" t="s">
@@ -11241,12 +11241,12 @@
         <v>132</v>
       </c>
       <c r="C54" s="202"/>
-      <c r="D54" s="428"/>
-      <c r="E54" s="429"/>
-      <c r="F54" s="430"/>
-      <c r="G54" s="267"/>
-      <c r="H54" s="268"/>
-      <c r="I54" s="269"/>
+      <c r="D54" s="319"/>
+      <c r="E54" s="320"/>
+      <c r="F54" s="321"/>
+      <c r="G54" s="294"/>
+      <c r="H54" s="295"/>
+      <c r="I54" s="296"/>
       <c r="J54" s="242"/>
       <c r="K54" s="243"/>
       <c r="L54" s="240"/>
@@ -11262,12 +11262,12 @@
         <v>134</v>
       </c>
       <c r="C55" s="202"/>
-      <c r="D55" s="428"/>
-      <c r="E55" s="429"/>
-      <c r="F55" s="430"/>
-      <c r="G55" s="267"/>
-      <c r="H55" s="268"/>
-      <c r="I55" s="269"/>
+      <c r="D55" s="319"/>
+      <c r="E55" s="320"/>
+      <c r="F55" s="321"/>
+      <c r="G55" s="294"/>
+      <c r="H55" s="295"/>
+      <c r="I55" s="296"/>
       <c r="J55" s="242"/>
       <c r="K55" s="243"/>
       <c r="L55" s="240"/>
@@ -11283,12 +11283,12 @@
         <v>136</v>
       </c>
       <c r="C56" s="202"/>
-      <c r="D56" s="428"/>
-      <c r="E56" s="429"/>
-      <c r="F56" s="430"/>
-      <c r="G56" s="267"/>
-      <c r="H56" s="268"/>
-      <c r="I56" s="269"/>
+      <c r="D56" s="319"/>
+      <c r="E56" s="320"/>
+      <c r="F56" s="321"/>
+      <c r="G56" s="294"/>
+      <c r="H56" s="295"/>
+      <c r="I56" s="296"/>
       <c r="J56" s="242"/>
       <c r="K56" s="243"/>
       <c r="L56" s="240"/>
@@ -11304,12 +11304,12 @@
         <v>138</v>
       </c>
       <c r="C57" s="202"/>
-      <c r="D57" s="428"/>
-      <c r="E57" s="429"/>
-      <c r="F57" s="430"/>
-      <c r="G57" s="267"/>
-      <c r="H57" s="268"/>
-      <c r="I57" s="269"/>
+      <c r="D57" s="319"/>
+      <c r="E57" s="320"/>
+      <c r="F57" s="321"/>
+      <c r="G57" s="294"/>
+      <c r="H57" s="295"/>
+      <c r="I57" s="296"/>
       <c r="J57" s="242"/>
       <c r="K57" s="243"/>
       <c r="L57" s="240"/>
@@ -11325,12 +11325,12 @@
         <v>140</v>
       </c>
       <c r="C58" s="204"/>
-      <c r="D58" s="431"/>
-      <c r="E58" s="432"/>
-      <c r="F58" s="433"/>
-      <c r="G58" s="414"/>
-      <c r="H58" s="415"/>
-      <c r="I58" s="416"/>
+      <c r="D58" s="322"/>
+      <c r="E58" s="323"/>
+      <c r="F58" s="324"/>
+      <c r="G58" s="310"/>
+      <c r="H58" s="311"/>
+      <c r="I58" s="312"/>
       <c r="J58" s="247"/>
       <c r="K58" s="248"/>
       <c r="L58" s="241"/>
@@ -11341,68 +11341,68 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="450" t="s">
+      <c r="A59" s="274" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="451"/>
-      <c r="C59" s="451"/>
-      <c r="D59" s="451"/>
-      <c r="E59" s="451"/>
-      <c r="F59" s="451"/>
-      <c r="G59" s="451"/>
-      <c r="H59" s="451"/>
-      <c r="I59" s="451"/>
-      <c r="J59" s="451"/>
-      <c r="K59" s="451"/>
-      <c r="L59" s="451"/>
-      <c r="M59" s="451"/>
-      <c r="N59" s="452"/>
+      <c r="B59" s="275"/>
+      <c r="C59" s="275"/>
+      <c r="D59" s="275"/>
+      <c r="E59" s="275"/>
+      <c r="F59" s="275"/>
+      <c r="G59" s="275"/>
+      <c r="H59" s="275"/>
+      <c r="I59" s="275"/>
+      <c r="J59" s="275"/>
+      <c r="K59" s="275"/>
+      <c r="L59" s="275"/>
+      <c r="M59" s="275"/>
+      <c r="N59" s="276"/>
       <c r="Q59" s="3" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="447" t="s">
+      <c r="A60" s="271" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="448"/>
-      <c r="C60" s="449"/>
-      <c r="D60" s="456" t="s">
+      <c r="B60" s="272"/>
+      <c r="C60" s="273"/>
+      <c r="D60" s="287" t="s">
         <v>144</v>
       </c>
-      <c r="E60" s="457"/>
-      <c r="F60" s="457"/>
-      <c r="G60" s="457"/>
-      <c r="H60" s="457"/>
-      <c r="I60" s="458"/>
-      <c r="J60" s="459" t="s">
+      <c r="E60" s="288"/>
+      <c r="F60" s="288"/>
+      <c r="G60" s="288"/>
+      <c r="H60" s="288"/>
+      <c r="I60" s="289"/>
+      <c r="J60" s="290" t="s">
         <v>145</v>
       </c>
-      <c r="K60" s="460"/>
-      <c r="L60" s="453"/>
-      <c r="M60" s="454"/>
-      <c r="N60" s="455"/>
+      <c r="K60" s="291"/>
+      <c r="L60" s="277"/>
+      <c r="M60" s="278"/>
+      <c r="N60" s="279"/>
       <c r="Q60" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="119" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="446" t="s">
+      <c r="A61" s="270" t="s">
         <v>404</v>
       </c>
-      <c r="B61" s="446"/>
-      <c r="C61" s="446"/>
-      <c r="D61" s="446"/>
-      <c r="E61" s="446"/>
-      <c r="F61" s="446"/>
-      <c r="G61" s="446"/>
-      <c r="H61" s="446"/>
-      <c r="I61" s="446"/>
-      <c r="J61" s="446"/>
-      <c r="K61" s="446"/>
-      <c r="L61" s="446"/>
-      <c r="M61" s="446"/>
-      <c r="N61" s="446"/>
+      <c r="B61" s="270"/>
+      <c r="C61" s="270"/>
+      <c r="D61" s="270"/>
+      <c r="E61" s="270"/>
+      <c r="F61" s="270"/>
+      <c r="G61" s="270"/>
+      <c r="H61" s="270"/>
+      <c r="I61" s="270"/>
+      <c r="J61" s="270"/>
+      <c r="K61" s="270"/>
+      <c r="L61" s="270"/>
+      <c r="M61" s="270"/>
+      <c r="N61" s="270"/>
       <c r="Q61" s="217" t="s">
         <v>147</v>
       </c>
@@ -15131,6 +15131,123 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="141">
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:N49"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="J51:K52"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="I19:K20"/>
+    <mergeCell ref="L19:N20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D25:F26"/>
+    <mergeCell ref="D27:F28"/>
+    <mergeCell ref="D29:F30"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="D17:F18"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C26"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="I31:N31"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="I50:N50"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="B51:C53"/>
+    <mergeCell ref="D51:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
     <mergeCell ref="A61:N61"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="A59:N59"/>
@@ -15155,123 +15272,6 @@
     <mergeCell ref="G51:I53"/>
     <mergeCell ref="G55:I55"/>
     <mergeCell ref="G56:I56"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="B51:C53"/>
-    <mergeCell ref="D51:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="N51:N53"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="I50:N50"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="E20:F21"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="D22:F23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C26"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="I31:N31"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="I19:K20"/>
-    <mergeCell ref="L19:N20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D25:F26"/>
-    <mergeCell ref="D27:F28"/>
-    <mergeCell ref="D29:F30"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="D17:F18"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:N49"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="J51:K52"/>
-    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -15780,68 +15780,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="495"/>
-      <c r="B1" s="496"/>
-      <c r="C1" s="496"/>
-      <c r="D1" s="496"/>
-      <c r="E1" s="496"/>
-      <c r="F1" s="496"/>
-      <c r="G1" s="496"/>
-      <c r="H1" s="496"/>
-      <c r="I1" s="496"/>
-      <c r="J1" s="496"/>
-      <c r="K1" s="497"/>
+      <c r="A1" s="472"/>
+      <c r="B1" s="473"/>
+      <c r="C1" s="473"/>
+      <c r="D1" s="473"/>
+      <c r="E1" s="473"/>
+      <c r="F1" s="473"/>
+      <c r="G1" s="473"/>
+      <c r="H1" s="473"/>
+      <c r="I1" s="473"/>
+      <c r="J1" s="473"/>
+      <c r="K1" s="474"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="506" t="s">
+      <c r="A2" s="485" t="s">
         <v>304</v>
       </c>
-      <c r="B2" s="507"/>
-      <c r="C2" s="507"/>
-      <c r="D2" s="507"/>
-      <c r="E2" s="507"/>
-      <c r="F2" s="507"/>
-      <c r="G2" s="507"/>
-      <c r="H2" s="507"/>
-      <c r="I2" s="507"/>
-      <c r="J2" s="507"/>
-      <c r="K2" s="508"/>
+      <c r="B2" s="486"/>
+      <c r="C2" s="486"/>
+      <c r="D2" s="486"/>
+      <c r="E2" s="486"/>
+      <c r="F2" s="486"/>
+      <c r="G2" s="486"/>
+      <c r="H2" s="486"/>
+      <c r="I2" s="486"/>
+      <c r="J2" s="486"/>
+      <c r="K2" s="487"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="116" t="s">
         <v>305</v>
       </c>
-      <c r="B3" s="498" t="s">
+      <c r="B3" s="475" t="s">
         <v>306</v>
       </c>
-      <c r="C3" s="498"/>
-      <c r="D3" s="498"/>
-      <c r="E3" s="499"/>
-      <c r="F3" s="504" t="s">
+      <c r="C3" s="475"/>
+      <c r="D3" s="475"/>
+      <c r="E3" s="476"/>
+      <c r="F3" s="483" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="500" t="s">
+      <c r="G3" s="479" t="s">
         <v>308</v>
       </c>
-      <c r="H3" s="499"/>
-      <c r="I3" s="500" t="s">
+      <c r="H3" s="476"/>
+      <c r="I3" s="479" t="s">
         <v>309</v>
       </c>
-      <c r="J3" s="502" t="s">
+      <c r="J3" s="481" t="s">
         <v>310</v>
       </c>
-      <c r="K3" s="503"/>
+      <c r="K3" s="482"/>
     </row>
     <row r="4" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="487"/>
-      <c r="C4" s="487"/>
-      <c r="D4" s="487"/>
-      <c r="E4" s="488"/>
-      <c r="F4" s="505"/>
-      <c r="G4" s="501"/>
-      <c r="H4" s="488"/>
-      <c r="I4" s="501"/>
+      <c r="B4" s="477"/>
+      <c r="C4" s="477"/>
+      <c r="D4" s="477"/>
+      <c r="E4" s="478"/>
+      <c r="F4" s="484"/>
+      <c r="G4" s="480"/>
+      <c r="H4" s="478"/>
+      <c r="I4" s="480"/>
       <c r="J4" s="5" t="s">
         <v>311</v>
       </c>
@@ -15850,125 +15850,125 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="511"/>
-      <c r="B5" s="469"/>
-      <c r="C5" s="469"/>
-      <c r="D5" s="469"/>
-      <c r="E5" s="469"/>
+      <c r="A5" s="491"/>
+      <c r="B5" s="492"/>
+      <c r="C5" s="492"/>
+      <c r="D5" s="492"/>
+      <c r="E5" s="492"/>
       <c r="F5" s="261"/>
-      <c r="G5" s="471"/>
-      <c r="H5" s="471"/>
+      <c r="G5" s="490"/>
+      <c r="H5" s="490"/>
       <c r="I5" s="262"/>
       <c r="J5" s="250"/>
       <c r="K5" s="263"/>
     </row>
     <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="511"/>
-      <c r="B6" s="469"/>
-      <c r="C6" s="469"/>
-      <c r="D6" s="469"/>
-      <c r="E6" s="469"/>
+      <c r="A6" s="491"/>
+      <c r="B6" s="492"/>
+      <c r="C6" s="492"/>
+      <c r="D6" s="492"/>
+      <c r="E6" s="492"/>
       <c r="F6" s="261"/>
-      <c r="G6" s="515"/>
-      <c r="H6" s="516"/>
+      <c r="G6" s="498"/>
+      <c r="H6" s="499"/>
       <c r="I6" s="262"/>
       <c r="J6" s="250"/>
       <c r="K6" s="263"/>
     </row>
     <row r="7" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="511"/>
-      <c r="B7" s="469"/>
-      <c r="C7" s="469"/>
-      <c r="D7" s="469"/>
-      <c r="E7" s="469"/>
+      <c r="A7" s="491"/>
+      <c r="B7" s="492"/>
+      <c r="C7" s="492"/>
+      <c r="D7" s="492"/>
+      <c r="E7" s="492"/>
       <c r="F7" s="261"/>
-      <c r="G7" s="471"/>
-      <c r="H7" s="471"/>
+      <c r="G7" s="490"/>
+      <c r="H7" s="490"/>
       <c r="I7" s="262"/>
       <c r="J7" s="250"/>
       <c r="K7" s="263"/>
     </row>
     <row r="8" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="511"/>
-      <c r="B8" s="469"/>
-      <c r="C8" s="469"/>
-      <c r="D8" s="469"/>
-      <c r="E8" s="469"/>
+      <c r="A8" s="491"/>
+      <c r="B8" s="492"/>
+      <c r="C8" s="492"/>
+      <c r="D8" s="492"/>
+      <c r="E8" s="492"/>
       <c r="F8" s="261"/>
-      <c r="G8" s="471"/>
-      <c r="H8" s="471"/>
+      <c r="G8" s="490"/>
+      <c r="H8" s="490"/>
       <c r="I8" s="262"/>
       <c r="J8" s="250"/>
       <c r="K8" s="263"/>
     </row>
     <row r="9" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="511"/>
-      <c r="B9" s="469"/>
-      <c r="C9" s="469"/>
-      <c r="D9" s="469"/>
-      <c r="E9" s="469"/>
+      <c r="A9" s="491"/>
+      <c r="B9" s="492"/>
+      <c r="C9" s="492"/>
+      <c r="D9" s="492"/>
+      <c r="E9" s="492"/>
       <c r="F9" s="261"/>
-      <c r="G9" s="471"/>
-      <c r="H9" s="471"/>
+      <c r="G9" s="490"/>
+      <c r="H9" s="490"/>
       <c r="I9" s="262"/>
       <c r="J9" s="250"/>
       <c r="K9" s="263"/>
     </row>
     <row r="10" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="511"/>
-      <c r="B10" s="469"/>
-      <c r="C10" s="469"/>
-      <c r="D10" s="469"/>
-      <c r="E10" s="469"/>
+      <c r="A10" s="491"/>
+      <c r="B10" s="492"/>
+      <c r="C10" s="492"/>
+      <c r="D10" s="492"/>
+      <c r="E10" s="492"/>
       <c r="F10" s="261"/>
-      <c r="G10" s="471"/>
-      <c r="H10" s="471"/>
+      <c r="G10" s="490"/>
+      <c r="H10" s="490"/>
       <c r="I10" s="262"/>
       <c r="J10" s="250"/>
       <c r="K10" s="263"/>
     </row>
     <row r="11" spans="1:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="484"/>
-      <c r="B11" s="476"/>
-      <c r="C11" s="476"/>
-      <c r="D11" s="476"/>
-      <c r="E11" s="476"/>
+      <c r="A11" s="504"/>
+      <c r="B11" s="505"/>
+      <c r="C11" s="505"/>
+      <c r="D11" s="505"/>
+      <c r="E11" s="505"/>
       <c r="F11" s="264"/>
-      <c r="G11" s="473"/>
-      <c r="H11" s="473"/>
+      <c r="G11" s="512"/>
+      <c r="H11" s="512"/>
       <c r="I11" s="265"/>
       <c r="J11" s="252"/>
       <c r="K11" s="266"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="489" t="s">
+      <c r="A12" s="506" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="490"/>
-      <c r="C12" s="490"/>
-      <c r="D12" s="490"/>
-      <c r="E12" s="490"/>
-      <c r="F12" s="490"/>
-      <c r="G12" s="490"/>
-      <c r="H12" s="490"/>
-      <c r="I12" s="490"/>
-      <c r="J12" s="490"/>
-      <c r="K12" s="491"/>
+      <c r="B12" s="507"/>
+      <c r="C12" s="507"/>
+      <c r="D12" s="507"/>
+      <c r="E12" s="507"/>
+      <c r="F12" s="507"/>
+      <c r="G12" s="507"/>
+      <c r="H12" s="507"/>
+      <c r="I12" s="507"/>
+      <c r="J12" s="507"/>
+      <c r="K12" s="508"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="492" t="s">
+      <c r="A13" s="509" t="s">
         <v>313</v>
       </c>
-      <c r="B13" s="493"/>
-      <c r="C13" s="493"/>
-      <c r="D13" s="493"/>
-      <c r="E13" s="493"/>
-      <c r="F13" s="493"/>
-      <c r="G13" s="493"/>
-      <c r="H13" s="493"/>
-      <c r="I13" s="493"/>
-      <c r="J13" s="493"/>
-      <c r="K13" s="494"/>
+      <c r="B13" s="510"/>
+      <c r="C13" s="510"/>
+      <c r="D13" s="510"/>
+      <c r="E13" s="510"/>
+      <c r="F13" s="510"/>
+      <c r="G13" s="510"/>
+      <c r="H13" s="510"/>
+      <c r="I13" s="510"/>
+      <c r="J13" s="510"/>
+      <c r="K13" s="511"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="183" t="s">
@@ -15989,449 +15989,449 @@
       <c r="A15" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B15" s="485" t="s">
+      <c r="B15" s="496" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="486"/>
-      <c r="D15" s="514" t="s">
+      <c r="C15" s="497"/>
+      <c r="D15" s="495" t="s">
         <v>316</v>
       </c>
-      <c r="E15" s="485"/>
-      <c r="F15" s="486"/>
-      <c r="G15" s="514" t="s">
+      <c r="E15" s="496"/>
+      <c r="F15" s="497"/>
+      <c r="G15" s="495" t="s">
         <v>317</v>
       </c>
-      <c r="H15" s="485"/>
-      <c r="I15" s="486"/>
-      <c r="J15" s="474" t="s">
+      <c r="H15" s="496"/>
+      <c r="I15" s="497"/>
+      <c r="J15" s="514" t="s">
         <v>318</v>
       </c>
-      <c r="K15" s="509" t="s">
+      <c r="K15" s="488" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="487"/>
-      <c r="C16" s="488"/>
-      <c r="D16" s="514"/>
-      <c r="E16" s="485"/>
-      <c r="F16" s="486"/>
-      <c r="G16" s="514"/>
-      <c r="H16" s="485"/>
-      <c r="I16" s="486"/>
-      <c r="J16" s="474"/>
-      <c r="K16" s="509"/>
+      <c r="B16" s="477"/>
+      <c r="C16" s="478"/>
+      <c r="D16" s="495"/>
+      <c r="E16" s="496"/>
+      <c r="F16" s="497"/>
+      <c r="G16" s="495"/>
+      <c r="H16" s="496"/>
+      <c r="I16" s="497"/>
+      <c r="J16" s="514"/>
+      <c r="K16" s="488"/>
     </row>
     <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="512" t="s">
+      <c r="A17" s="493" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="513"/>
+      <c r="B17" s="494"/>
       <c r="C17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="501"/>
-      <c r="E17" s="487"/>
-      <c r="F17" s="488"/>
-      <c r="G17" s="501"/>
-      <c r="H17" s="487"/>
-      <c r="I17" s="488"/>
-      <c r="J17" s="475"/>
-      <c r="K17" s="510"/>
+      <c r="D17" s="480"/>
+      <c r="E17" s="477"/>
+      <c r="F17" s="478"/>
+      <c r="G17" s="480"/>
+      <c r="H17" s="477"/>
+      <c r="I17" s="478"/>
+      <c r="J17" s="515"/>
+      <c r="K17" s="489"/>
     </row>
     <row r="18" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="470"/>
-      <c r="B18" s="471"/>
+      <c r="A18" s="503"/>
+      <c r="B18" s="490"/>
       <c r="C18" s="254"/>
-      <c r="D18" s="469"/>
-      <c r="E18" s="469"/>
-      <c r="F18" s="469"/>
-      <c r="G18" s="469"/>
-      <c r="H18" s="469"/>
-      <c r="I18" s="469"/>
+      <c r="D18" s="492"/>
+      <c r="E18" s="492"/>
+      <c r="F18" s="492"/>
+      <c r="G18" s="492"/>
+      <c r="H18" s="492"/>
+      <c r="I18" s="492"/>
       <c r="J18" s="250"/>
       <c r="K18" s="251"/>
     </row>
     <row r="19" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="470"/>
-      <c r="B19" s="471"/>
+      <c r="A19" s="503"/>
+      <c r="B19" s="490"/>
       <c r="C19" s="254"/>
-      <c r="D19" s="469"/>
-      <c r="E19" s="469"/>
-      <c r="F19" s="469"/>
-      <c r="G19" s="469"/>
-      <c r="H19" s="469"/>
-      <c r="I19" s="469"/>
+      <c r="D19" s="492"/>
+      <c r="E19" s="492"/>
+      <c r="F19" s="492"/>
+      <c r="G19" s="492"/>
+      <c r="H19" s="492"/>
+      <c r="I19" s="492"/>
       <c r="J19" s="250"/>
       <c r="K19" s="251"/>
     </row>
     <row r="20" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="470"/>
-      <c r="B20" s="471"/>
+      <c r="A20" s="503"/>
+      <c r="B20" s="490"/>
       <c r="C20" s="254"/>
-      <c r="D20" s="469"/>
-      <c r="E20" s="469"/>
-      <c r="F20" s="469"/>
-      <c r="G20" s="469"/>
-      <c r="H20" s="469"/>
-      <c r="I20" s="469"/>
+      <c r="D20" s="492"/>
+      <c r="E20" s="492"/>
+      <c r="F20" s="492"/>
+      <c r="G20" s="492"/>
+      <c r="H20" s="492"/>
+      <c r="I20" s="492"/>
       <c r="J20" s="250"/>
       <c r="K20" s="251"/>
     </row>
     <row r="21" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="470"/>
-      <c r="B21" s="471"/>
+      <c r="A21" s="503"/>
+      <c r="B21" s="490"/>
       <c r="C21" s="254"/>
-      <c r="D21" s="469"/>
-      <c r="E21" s="469"/>
-      <c r="F21" s="469"/>
-      <c r="G21" s="469"/>
-      <c r="H21" s="469"/>
-      <c r="I21" s="469"/>
+      <c r="D21" s="492"/>
+      <c r="E21" s="492"/>
+      <c r="F21" s="492"/>
+      <c r="G21" s="492"/>
+      <c r="H21" s="492"/>
+      <c r="I21" s="492"/>
       <c r="J21" s="250"/>
       <c r="K21" s="251"/>
     </row>
     <row r="22" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="470"/>
-      <c r="B22" s="471"/>
+      <c r="A22" s="503"/>
+      <c r="B22" s="490"/>
       <c r="C22" s="254"/>
-      <c r="D22" s="469"/>
-      <c r="E22" s="469"/>
-      <c r="F22" s="469"/>
-      <c r="G22" s="469"/>
-      <c r="H22" s="469"/>
-      <c r="I22" s="469"/>
+      <c r="D22" s="492"/>
+      <c r="E22" s="492"/>
+      <c r="F22" s="492"/>
+      <c r="G22" s="492"/>
+      <c r="H22" s="492"/>
+      <c r="I22" s="492"/>
       <c r="J22" s="250"/>
       <c r="K22" s="251"/>
     </row>
     <row r="23" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="470"/>
-      <c r="B23" s="471"/>
+      <c r="A23" s="503"/>
+      <c r="B23" s="490"/>
       <c r="C23" s="254"/>
-      <c r="D23" s="469"/>
-      <c r="E23" s="469"/>
-      <c r="F23" s="469"/>
-      <c r="G23" s="469"/>
-      <c r="H23" s="469"/>
-      <c r="I23" s="469"/>
+      <c r="D23" s="492"/>
+      <c r="E23" s="492"/>
+      <c r="F23" s="492"/>
+      <c r="G23" s="492"/>
+      <c r="H23" s="492"/>
+      <c r="I23" s="492"/>
       <c r="J23" s="250"/>
       <c r="K23" s="251"/>
     </row>
     <row r="24" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="470"/>
-      <c r="B24" s="471"/>
+      <c r="A24" s="503"/>
+      <c r="B24" s="490"/>
       <c r="C24" s="254"/>
-      <c r="D24" s="469"/>
-      <c r="E24" s="469"/>
-      <c r="F24" s="469"/>
-      <c r="G24" s="469"/>
-      <c r="H24" s="469"/>
-      <c r="I24" s="469"/>
+      <c r="D24" s="492"/>
+      <c r="E24" s="492"/>
+      <c r="F24" s="492"/>
+      <c r="G24" s="492"/>
+      <c r="H24" s="492"/>
+      <c r="I24" s="492"/>
       <c r="J24" s="250"/>
       <c r="K24" s="251"/>
     </row>
     <row r="25" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="470"/>
-      <c r="B25" s="471"/>
+      <c r="A25" s="503"/>
+      <c r="B25" s="490"/>
       <c r="C25" s="254"/>
-      <c r="D25" s="469"/>
-      <c r="E25" s="469"/>
-      <c r="F25" s="469"/>
-      <c r="G25" s="469"/>
-      <c r="H25" s="469"/>
-      <c r="I25" s="469"/>
+      <c r="D25" s="492"/>
+      <c r="E25" s="492"/>
+      <c r="F25" s="492"/>
+      <c r="G25" s="492"/>
+      <c r="H25" s="492"/>
+      <c r="I25" s="492"/>
       <c r="J25" s="250"/>
       <c r="K25" s="251"/>
     </row>
     <row r="26" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="470"/>
-      <c r="B26" s="471"/>
+      <c r="A26" s="503"/>
+      <c r="B26" s="490"/>
       <c r="C26" s="254"/>
-      <c r="D26" s="469"/>
-      <c r="E26" s="469"/>
-      <c r="F26" s="469"/>
-      <c r="G26" s="469"/>
-      <c r="H26" s="469"/>
-      <c r="I26" s="469"/>
+      <c r="D26" s="492"/>
+      <c r="E26" s="492"/>
+      <c r="F26" s="492"/>
+      <c r="G26" s="492"/>
+      <c r="H26" s="492"/>
+      <c r="I26" s="492"/>
       <c r="J26" s="250"/>
       <c r="K26" s="251"/>
     </row>
     <row r="27" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="470"/>
-      <c r="B27" s="471"/>
+      <c r="A27" s="503"/>
+      <c r="B27" s="490"/>
       <c r="C27" s="254"/>
-      <c r="D27" s="469"/>
-      <c r="E27" s="469"/>
-      <c r="F27" s="469"/>
-      <c r="G27" s="469"/>
-      <c r="H27" s="469"/>
-      <c r="I27" s="469"/>
+      <c r="D27" s="492"/>
+      <c r="E27" s="492"/>
+      <c r="F27" s="492"/>
+      <c r="G27" s="492"/>
+      <c r="H27" s="492"/>
+      <c r="I27" s="492"/>
       <c r="J27" s="250"/>
       <c r="K27" s="251"/>
     </row>
     <row r="28" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="470"/>
-      <c r="B28" s="471"/>
+      <c r="A28" s="503"/>
+      <c r="B28" s="490"/>
       <c r="C28" s="254"/>
-      <c r="D28" s="469"/>
-      <c r="E28" s="469"/>
-      <c r="F28" s="469"/>
-      <c r="G28" s="469"/>
-      <c r="H28" s="469"/>
-      <c r="I28" s="469"/>
+      <c r="D28" s="492"/>
+      <c r="E28" s="492"/>
+      <c r="F28" s="492"/>
+      <c r="G28" s="492"/>
+      <c r="H28" s="492"/>
+      <c r="I28" s="492"/>
       <c r="J28" s="250"/>
       <c r="K28" s="251"/>
     </row>
     <row r="29" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="470"/>
-      <c r="B29" s="471"/>
+      <c r="A29" s="503"/>
+      <c r="B29" s="490"/>
       <c r="C29" s="254"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
-      <c r="G29" s="469"/>
-      <c r="H29" s="469"/>
-      <c r="I29" s="469"/>
+      <c r="D29" s="492"/>
+      <c r="E29" s="492"/>
+      <c r="F29" s="492"/>
+      <c r="G29" s="492"/>
+      <c r="H29" s="492"/>
+      <c r="I29" s="492"/>
       <c r="J29" s="250"/>
       <c r="K29" s="251"/>
     </row>
     <row r="30" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="470"/>
-      <c r="B30" s="471"/>
+      <c r="A30" s="503"/>
+      <c r="B30" s="490"/>
       <c r="C30" s="254"/>
-      <c r="D30" s="469"/>
-      <c r="E30" s="469"/>
-      <c r="F30" s="469"/>
-      <c r="G30" s="469"/>
-      <c r="H30" s="469"/>
-      <c r="I30" s="469"/>
+      <c r="D30" s="492"/>
+      <c r="E30" s="492"/>
+      <c r="F30" s="492"/>
+      <c r="G30" s="492"/>
+      <c r="H30" s="492"/>
+      <c r="I30" s="492"/>
       <c r="J30" s="250"/>
       <c r="K30" s="251"/>
     </row>
     <row r="31" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="470"/>
-      <c r="B31" s="471"/>
+      <c r="A31" s="503"/>
+      <c r="B31" s="490"/>
       <c r="C31" s="254"/>
-      <c r="D31" s="469"/>
-      <c r="E31" s="469"/>
-      <c r="F31" s="469"/>
-      <c r="G31" s="469"/>
-      <c r="H31" s="469"/>
-      <c r="I31" s="469"/>
+      <c r="D31" s="492"/>
+      <c r="E31" s="492"/>
+      <c r="F31" s="492"/>
+      <c r="G31" s="492"/>
+      <c r="H31" s="492"/>
+      <c r="I31" s="492"/>
       <c r="J31" s="250"/>
       <c r="K31" s="251"/>
     </row>
     <row r="32" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="470"/>
-      <c r="B32" s="471"/>
+      <c r="A32" s="503"/>
+      <c r="B32" s="490"/>
       <c r="C32" s="254"/>
-      <c r="D32" s="469"/>
-      <c r="E32" s="469"/>
-      <c r="F32" s="469"/>
-      <c r="G32" s="469"/>
-      <c r="H32" s="469"/>
-      <c r="I32" s="469"/>
+      <c r="D32" s="492"/>
+      <c r="E32" s="492"/>
+      <c r="F32" s="492"/>
+      <c r="G32" s="492"/>
+      <c r="H32" s="492"/>
+      <c r="I32" s="492"/>
       <c r="J32" s="250"/>
       <c r="K32" s="251"/>
     </row>
     <row r="33" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="470"/>
-      <c r="B33" s="471"/>
+      <c r="A33" s="503"/>
+      <c r="B33" s="490"/>
       <c r="C33" s="254"/>
-      <c r="D33" s="469"/>
-      <c r="E33" s="469"/>
-      <c r="F33" s="469"/>
-      <c r="G33" s="469"/>
-      <c r="H33" s="469"/>
-      <c r="I33" s="469"/>
+      <c r="D33" s="492"/>
+      <c r="E33" s="492"/>
+      <c r="F33" s="492"/>
+      <c r="G33" s="492"/>
+      <c r="H33" s="492"/>
+      <c r="I33" s="492"/>
       <c r="J33" s="250"/>
       <c r="K33" s="251"/>
     </row>
     <row r="34" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="470"/>
-      <c r="B34" s="471"/>
+      <c r="A34" s="503"/>
+      <c r="B34" s="490"/>
       <c r="C34" s="254"/>
-      <c r="D34" s="469"/>
-      <c r="E34" s="469"/>
-      <c r="F34" s="469"/>
-      <c r="G34" s="469"/>
-      <c r="H34" s="469"/>
-      <c r="I34" s="469"/>
+      <c r="D34" s="492"/>
+      <c r="E34" s="492"/>
+      <c r="F34" s="492"/>
+      <c r="G34" s="492"/>
+      <c r="H34" s="492"/>
+      <c r="I34" s="492"/>
       <c r="J34" s="250"/>
       <c r="K34" s="251"/>
     </row>
     <row r="35" spans="1:12" s="8" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="470"/>
-      <c r="B35" s="471"/>
+      <c r="A35" s="503"/>
+      <c r="B35" s="490"/>
       <c r="C35" s="254"/>
-      <c r="D35" s="469"/>
-      <c r="E35" s="469"/>
-      <c r="F35" s="469"/>
-      <c r="G35" s="469"/>
-      <c r="H35" s="469"/>
-      <c r="I35" s="469"/>
+      <c r="D35" s="492"/>
+      <c r="E35" s="492"/>
+      <c r="F35" s="492"/>
+      <c r="G35" s="492"/>
+      <c r="H35" s="492"/>
+      <c r="I35" s="492"/>
       <c r="J35" s="250"/>
       <c r="K35" s="251"/>
     </row>
     <row r="36" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="470"/>
-      <c r="B36" s="471"/>
+      <c r="A36" s="503"/>
+      <c r="B36" s="490"/>
       <c r="C36" s="254"/>
-      <c r="D36" s="469"/>
-      <c r="E36" s="469"/>
-      <c r="F36" s="469"/>
-      <c r="G36" s="469"/>
-      <c r="H36" s="469"/>
-      <c r="I36" s="469"/>
+      <c r="D36" s="492"/>
+      <c r="E36" s="492"/>
+      <c r="F36" s="492"/>
+      <c r="G36" s="492"/>
+      <c r="H36" s="492"/>
+      <c r="I36" s="492"/>
       <c r="J36" s="250"/>
       <c r="K36" s="251"/>
     </row>
     <row r="37" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="470"/>
-      <c r="B37" s="471"/>
+      <c r="A37" s="503"/>
+      <c r="B37" s="490"/>
       <c r="C37" s="254"/>
-      <c r="D37" s="469"/>
-      <c r="E37" s="469"/>
-      <c r="F37" s="469"/>
-      <c r="G37" s="469"/>
-      <c r="H37" s="469"/>
-      <c r="I37" s="469"/>
+      <c r="D37" s="492"/>
+      <c r="E37" s="492"/>
+      <c r="F37" s="492"/>
+      <c r="G37" s="492"/>
+      <c r="H37" s="492"/>
+      <c r="I37" s="492"/>
       <c r="J37" s="250"/>
       <c r="K37" s="251"/>
     </row>
     <row r="38" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="470"/>
-      <c r="B38" s="471"/>
+      <c r="A38" s="503"/>
+      <c r="B38" s="490"/>
       <c r="C38" s="254"/>
-      <c r="D38" s="469"/>
-      <c r="E38" s="469"/>
-      <c r="F38" s="469"/>
-      <c r="G38" s="469"/>
-      <c r="H38" s="469"/>
-      <c r="I38" s="469"/>
+      <c r="D38" s="492"/>
+      <c r="E38" s="492"/>
+      <c r="F38" s="492"/>
+      <c r="G38" s="492"/>
+      <c r="H38" s="492"/>
+      <c r="I38" s="492"/>
       <c r="J38" s="250"/>
       <c r="K38" s="251"/>
     </row>
     <row r="39" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="470"/>
-      <c r="B39" s="471"/>
+      <c r="A39" s="503"/>
+      <c r="B39" s="490"/>
       <c r="C39" s="254"/>
-      <c r="D39" s="469"/>
-      <c r="E39" s="469"/>
-      <c r="F39" s="469"/>
-      <c r="G39" s="469"/>
-      <c r="H39" s="469"/>
-      <c r="I39" s="469"/>
+      <c r="D39" s="492"/>
+      <c r="E39" s="492"/>
+      <c r="F39" s="492"/>
+      <c r="G39" s="492"/>
+      <c r="H39" s="492"/>
+      <c r="I39" s="492"/>
       <c r="J39" s="250"/>
       <c r="K39" s="251"/>
     </row>
     <row r="40" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="470"/>
-      <c r="B40" s="471"/>
+      <c r="A40" s="503"/>
+      <c r="B40" s="490"/>
       <c r="C40" s="254"/>
-      <c r="D40" s="469"/>
-      <c r="E40" s="469"/>
-      <c r="F40" s="469"/>
-      <c r="G40" s="469"/>
-      <c r="H40" s="469"/>
-      <c r="I40" s="469"/>
+      <c r="D40" s="492"/>
+      <c r="E40" s="492"/>
+      <c r="F40" s="492"/>
+      <c r="G40" s="492"/>
+      <c r="H40" s="492"/>
+      <c r="I40" s="492"/>
       <c r="J40" s="250"/>
       <c r="K40" s="251"/>
     </row>
     <row r="41" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="470"/>
-      <c r="B41" s="471"/>
+      <c r="A41" s="503"/>
+      <c r="B41" s="490"/>
       <c r="C41" s="254"/>
-      <c r="D41" s="469"/>
-      <c r="E41" s="469"/>
-      <c r="F41" s="469"/>
-      <c r="G41" s="469"/>
-      <c r="H41" s="469"/>
-      <c r="I41" s="469"/>
+      <c r="D41" s="492"/>
+      <c r="E41" s="492"/>
+      <c r="F41" s="492"/>
+      <c r="G41" s="492"/>
+      <c r="H41" s="492"/>
+      <c r="I41" s="492"/>
       <c r="J41" s="250"/>
       <c r="K41" s="251"/>
     </row>
     <row r="42" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="470"/>
-      <c r="B42" s="471"/>
+      <c r="A42" s="503"/>
+      <c r="B42" s="490"/>
       <c r="C42" s="254"/>
-      <c r="D42" s="469"/>
-      <c r="E42" s="469"/>
-      <c r="F42" s="469"/>
-      <c r="G42" s="469"/>
-      <c r="H42" s="469"/>
-      <c r="I42" s="469"/>
+      <c r="D42" s="492"/>
+      <c r="E42" s="492"/>
+      <c r="F42" s="492"/>
+      <c r="G42" s="492"/>
+      <c r="H42" s="492"/>
+      <c r="I42" s="492"/>
       <c r="J42" s="250"/>
       <c r="K42" s="251"/>
     </row>
     <row r="43" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="470"/>
-      <c r="B43" s="471"/>
+      <c r="A43" s="503"/>
+      <c r="B43" s="490"/>
       <c r="C43" s="254"/>
-      <c r="D43" s="469"/>
-      <c r="E43" s="469"/>
-      <c r="F43" s="469"/>
-      <c r="G43" s="469"/>
-      <c r="H43" s="469"/>
-      <c r="I43" s="469"/>
+      <c r="D43" s="492"/>
+      <c r="E43" s="492"/>
+      <c r="F43" s="492"/>
+      <c r="G43" s="492"/>
+      <c r="H43" s="492"/>
+      <c r="I43" s="492"/>
       <c r="J43" s="250"/>
       <c r="K43" s="251"/>
     </row>
     <row r="44" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="470"/>
-      <c r="B44" s="471"/>
+      <c r="A44" s="503"/>
+      <c r="B44" s="490"/>
       <c r="C44" s="254"/>
-      <c r="D44" s="469"/>
-      <c r="E44" s="469"/>
-      <c r="F44" s="469"/>
-      <c r="G44" s="469"/>
-      <c r="H44" s="469"/>
-      <c r="I44" s="469"/>
+      <c r="D44" s="492"/>
+      <c r="E44" s="492"/>
+      <c r="F44" s="492"/>
+      <c r="G44" s="492"/>
+      <c r="H44" s="492"/>
+      <c r="I44" s="492"/>
       <c r="J44" s="250"/>
       <c r="K44" s="251"/>
     </row>
     <row r="45" spans="1:12" s="8" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="472"/>
-      <c r="B45" s="473"/>
+      <c r="A45" s="513"/>
+      <c r="B45" s="512"/>
       <c r="C45" s="255"/>
-      <c r="D45" s="476"/>
-      <c r="E45" s="476"/>
-      <c r="F45" s="476"/>
-      <c r="G45" s="476"/>
-      <c r="H45" s="476"/>
-      <c r="I45" s="476"/>
+      <c r="D45" s="505"/>
+      <c r="E45" s="505"/>
+      <c r="F45" s="505"/>
+      <c r="G45" s="505"/>
+      <c r="H45" s="505"/>
+      <c r="I45" s="505"/>
       <c r="J45" s="252"/>
       <c r="K45" s="253"/>
     </row>
     <row r="46" spans="1:12" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="477" t="s">
+      <c r="A46" s="516" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="478"/>
-      <c r="C46" s="478"/>
-      <c r="D46" s="478"/>
-      <c r="E46" s="478"/>
-      <c r="F46" s="478"/>
-      <c r="G46" s="478"/>
-      <c r="H46" s="478"/>
-      <c r="I46" s="478"/>
-      <c r="J46" s="479"/>
-      <c r="K46" s="480"/>
+      <c r="B46" s="517"/>
+      <c r="C46" s="517"/>
+      <c r="D46" s="517"/>
+      <c r="E46" s="517"/>
+      <c r="F46" s="517"/>
+      <c r="G46" s="517"/>
+      <c r="H46" s="517"/>
+      <c r="I46" s="517"/>
+      <c r="J46" s="518"/>
+      <c r="K46" s="519"/>
     </row>
     <row r="47" spans="1:12" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="447" t="s">
+      <c r="A47" s="271" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="448"/>
-      <c r="C47" s="449"/>
-      <c r="D47" s="481" t="s">
+      <c r="B47" s="272"/>
+      <c r="C47" s="273"/>
+      <c r="D47" s="500" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="482"/>
-      <c r="F47" s="482"/>
-      <c r="G47" s="482"/>
-      <c r="H47" s="483"/>
+      <c r="E47" s="501"/>
+      <c r="F47" s="501"/>
+      <c r="G47" s="501"/>
+      <c r="H47" s="502"/>
       <c r="I47" s="213" t="s">
         <v>145</v>
       </c>
@@ -16440,19 +16440,19 @@
       <c r="L47" s="215"/>
     </row>
     <row r="48" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="446" t="s">
+      <c r="A48" s="270" t="s">
         <v>403</v>
       </c>
-      <c r="B48" s="446"/>
-      <c r="C48" s="446"/>
-      <c r="D48" s="446"/>
-      <c r="E48" s="446"/>
-      <c r="F48" s="446"/>
-      <c r="G48" s="446"/>
-      <c r="H48" s="446"/>
-      <c r="I48" s="446"/>
-      <c r="J48" s="446"/>
-      <c r="K48" s="446"/>
+      <c r="B48" s="270"/>
+      <c r="C48" s="270"/>
+      <c r="D48" s="270"/>
+      <c r="E48" s="270"/>
+      <c r="F48" s="270"/>
+      <c r="G48" s="270"/>
+      <c r="H48" s="270"/>
+      <c r="I48" s="270"/>
+      <c r="J48" s="270"/>
+      <c r="K48" s="270"/>
       <c r="L48" s="218"/>
     </row>
   </sheetData>
@@ -16466,29 +16466,76 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="117">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B3:E4"/>
-    <mergeCell ref="G3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="K15:K17"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D15:F17"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="G15:I17"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G25:I25"/>
     <mergeCell ref="A48:K48"/>
     <mergeCell ref="D47:H47"/>
     <mergeCell ref="G43:I43"/>
@@ -16513,76 +16560,29 @@
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B3:E4"/>
+    <mergeCell ref="G3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D15:F17"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="G15:I17"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -16614,564 +16614,564 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="535"/>
-      <c r="B1" s="536"/>
-      <c r="C1" s="536"/>
-      <c r="D1" s="536"/>
-      <c r="E1" s="536"/>
-      <c r="F1" s="536"/>
-      <c r="G1" s="536"/>
-      <c r="H1" s="536"/>
-      <c r="I1" s="536"/>
-      <c r="J1" s="536"/>
-      <c r="K1" s="537"/>
+      <c r="A1" s="551"/>
+      <c r="B1" s="552"/>
+      <c r="C1" s="552"/>
+      <c r="D1" s="552"/>
+      <c r="E1" s="552"/>
+      <c r="F1" s="552"/>
+      <c r="G1" s="552"/>
+      <c r="H1" s="552"/>
+      <c r="I1" s="552"/>
+      <c r="J1" s="552"/>
+      <c r="K1" s="553"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="553" t="s">
+      <c r="A2" s="573" t="s">
         <v>320</v>
       </c>
-      <c r="B2" s="554"/>
-      <c r="C2" s="554"/>
-      <c r="D2" s="554"/>
-      <c r="E2" s="554"/>
-      <c r="F2" s="554"/>
-      <c r="G2" s="554"/>
-      <c r="H2" s="554"/>
-      <c r="I2" s="554"/>
-      <c r="J2" s="554"/>
-      <c r="K2" s="555"/>
+      <c r="B2" s="574"/>
+      <c r="C2" s="574"/>
+      <c r="D2" s="574"/>
+      <c r="E2" s="574"/>
+      <c r="F2" s="574"/>
+      <c r="G2" s="574"/>
+      <c r="H2" s="574"/>
+      <c r="I2" s="574"/>
+      <c r="J2" s="574"/>
+      <c r="K2" s="575"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="543" t="s">
+      <c r="A3" s="559" t="s">
         <v>321</v>
       </c>
-      <c r="B3" s="544" t="s">
+      <c r="B3" s="561" t="s">
         <v>322</v>
       </c>
-      <c r="C3" s="544"/>
-      <c r="D3" s="545"/>
-      <c r="E3" s="498" t="s">
+      <c r="C3" s="561"/>
+      <c r="D3" s="562"/>
+      <c r="E3" s="475" t="s">
         <v>323</v>
       </c>
-      <c r="F3" s="499"/>
-      <c r="G3" s="558" t="s">
+      <c r="F3" s="476"/>
+      <c r="G3" s="578" t="s">
         <v>324</v>
       </c>
-      <c r="H3" s="500" t="s">
+      <c r="H3" s="479" t="s">
         <v>325</v>
       </c>
-      <c r="I3" s="548"/>
-      <c r="J3" s="548"/>
-      <c r="K3" s="549"/>
+      <c r="I3" s="568"/>
+      <c r="J3" s="568"/>
+      <c r="K3" s="569"/>
     </row>
     <row r="4" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="534"/>
-      <c r="B4" s="546"/>
-      <c r="C4" s="546"/>
-      <c r="D4" s="547"/>
-      <c r="E4" s="487"/>
-      <c r="F4" s="488"/>
-      <c r="G4" s="559"/>
-      <c r="H4" s="550"/>
-      <c r="I4" s="538"/>
-      <c r="J4" s="538"/>
-      <c r="K4" s="551"/>
+      <c r="A4" s="560"/>
+      <c r="B4" s="563"/>
+      <c r="C4" s="563"/>
+      <c r="D4" s="564"/>
+      <c r="E4" s="477"/>
+      <c r="F4" s="478"/>
+      <c r="G4" s="579"/>
+      <c r="H4" s="570"/>
+      <c r="I4" s="554"/>
+      <c r="J4" s="554"/>
+      <c r="K4" s="571"/>
     </row>
     <row r="5" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
-      <c r="B5" s="556"/>
-      <c r="C5" s="556"/>
-      <c r="D5" s="557"/>
+      <c r="B5" s="576"/>
+      <c r="C5" s="576"/>
+      <c r="D5" s="577"/>
       <c r="E5" s="10" t="s">
         <v>129</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="560"/>
-      <c r="H5" s="552"/>
-      <c r="I5" s="435"/>
-      <c r="J5" s="435"/>
-      <c r="K5" s="436"/>
+      <c r="G5" s="580"/>
+      <c r="H5" s="572"/>
+      <c r="I5" s="326"/>
+      <c r="J5" s="326"/>
+      <c r="K5" s="327"/>
     </row>
     <row r="6" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="719"/>
-      <c r="B6" s="720"/>
-      <c r="C6" s="720"/>
-      <c r="D6" s="721"/>
-      <c r="E6" s="722"/>
-      <c r="F6" s="722"/>
-      <c r="G6" s="723"/>
-      <c r="H6" s="724"/>
-      <c r="I6" s="725"/>
-      <c r="J6" s="725"/>
-      <c r="K6" s="726"/>
+      <c r="A6" s="546"/>
+      <c r="B6" s="547"/>
+      <c r="C6" s="547"/>
+      <c r="D6" s="548"/>
+      <c r="E6" s="267"/>
+      <c r="F6" s="267"/>
+      <c r="G6" s="268"/>
+      <c r="H6" s="541"/>
+      <c r="I6" s="542"/>
+      <c r="J6" s="542"/>
+      <c r="K6" s="543"/>
     </row>
     <row r="7" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="719"/>
-      <c r="B7" s="720"/>
-      <c r="C7" s="720"/>
-      <c r="D7" s="721"/>
-      <c r="E7" s="722"/>
-      <c r="F7" s="722"/>
-      <c r="G7" s="723"/>
-      <c r="H7" s="724"/>
-      <c r="I7" s="725"/>
-      <c r="J7" s="725"/>
-      <c r="K7" s="726"/>
+      <c r="A7" s="546"/>
+      <c r="B7" s="547"/>
+      <c r="C7" s="547"/>
+      <c r="D7" s="548"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="268"/>
+      <c r="H7" s="541"/>
+      <c r="I7" s="542"/>
+      <c r="J7" s="542"/>
+      <c r="K7" s="543"/>
     </row>
     <row r="8" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="719"/>
-      <c r="B8" s="720"/>
-      <c r="C8" s="720"/>
-      <c r="D8" s="721"/>
-      <c r="E8" s="722"/>
-      <c r="F8" s="722"/>
-      <c r="G8" s="723"/>
-      <c r="H8" s="724"/>
-      <c r="I8" s="725"/>
-      <c r="J8" s="725"/>
-      <c r="K8" s="726"/>
+      <c r="A8" s="546"/>
+      <c r="B8" s="547"/>
+      <c r="C8" s="547"/>
+      <c r="D8" s="548"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="268"/>
+      <c r="H8" s="541"/>
+      <c r="I8" s="542"/>
+      <c r="J8" s="542"/>
+      <c r="K8" s="543"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="719"/>
-      <c r="B9" s="720"/>
-      <c r="C9" s="720"/>
-      <c r="D9" s="721"/>
-      <c r="E9" s="722"/>
-      <c r="F9" s="722"/>
-      <c r="G9" s="723"/>
-      <c r="H9" s="724"/>
-      <c r="I9" s="725"/>
-      <c r="J9" s="725"/>
-      <c r="K9" s="726"/>
+      <c r="A9" s="546"/>
+      <c r="B9" s="547"/>
+      <c r="C9" s="547"/>
+      <c r="D9" s="548"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="268"/>
+      <c r="H9" s="541"/>
+      <c r="I9" s="542"/>
+      <c r="J9" s="542"/>
+      <c r="K9" s="543"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="719"/>
-      <c r="B10" s="720"/>
-      <c r="C10" s="720"/>
-      <c r="D10" s="721"/>
-      <c r="E10" s="722"/>
-      <c r="F10" s="722"/>
-      <c r="G10" s="723"/>
-      <c r="H10" s="724"/>
-      <c r="I10" s="725"/>
-      <c r="J10" s="725"/>
-      <c r="K10" s="726"/>
+      <c r="A10" s="546"/>
+      <c r="B10" s="547"/>
+      <c r="C10" s="547"/>
+      <c r="D10" s="548"/>
+      <c r="E10" s="267"/>
+      <c r="F10" s="267"/>
+      <c r="G10" s="268"/>
+      <c r="H10" s="541"/>
+      <c r="I10" s="542"/>
+      <c r="J10" s="542"/>
+      <c r="K10" s="543"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="719"/>
-      <c r="B11" s="720"/>
-      <c r="C11" s="720"/>
-      <c r="D11" s="721"/>
-      <c r="E11" s="722"/>
-      <c r="F11" s="722"/>
-      <c r="G11" s="723"/>
-      <c r="H11" s="724"/>
-      <c r="I11" s="725"/>
-      <c r="J11" s="725"/>
-      <c r="K11" s="726"/>
+      <c r="A11" s="546"/>
+      <c r="B11" s="547"/>
+      <c r="C11" s="547"/>
+      <c r="D11" s="548"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="268"/>
+      <c r="H11" s="541"/>
+      <c r="I11" s="542"/>
+      <c r="J11" s="542"/>
+      <c r="K11" s="543"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="727"/>
-      <c r="B12" s="728"/>
-      <c r="C12" s="728"/>
-      <c r="D12" s="729"/>
-      <c r="E12" s="722"/>
-      <c r="F12" s="722"/>
-      <c r="G12" s="730"/>
-      <c r="H12" s="731"/>
-      <c r="I12" s="732"/>
-      <c r="J12" s="732"/>
-      <c r="K12" s="733"/>
+      <c r="A12" s="565"/>
+      <c r="B12" s="566"/>
+      <c r="C12" s="566"/>
+      <c r="D12" s="567"/>
+      <c r="E12" s="267"/>
+      <c r="F12" s="267"/>
+      <c r="G12" s="269"/>
+      <c r="H12" s="581"/>
+      <c r="I12" s="582"/>
+      <c r="J12" s="582"/>
+      <c r="K12" s="583"/>
     </row>
     <row r="13" spans="1:11" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="489" t="s">
+      <c r="A13" s="506" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="490"/>
-      <c r="C13" s="490"/>
-      <c r="D13" s="490"/>
-      <c r="E13" s="490"/>
-      <c r="F13" s="490"/>
-      <c r="G13" s="490"/>
-      <c r="H13" s="490"/>
-      <c r="I13" s="490"/>
-      <c r="J13" s="490"/>
-      <c r="K13" s="491"/>
+      <c r="B13" s="507"/>
+      <c r="C13" s="507"/>
+      <c r="D13" s="507"/>
+      <c r="E13" s="507"/>
+      <c r="F13" s="507"/>
+      <c r="G13" s="507"/>
+      <c r="H13" s="507"/>
+      <c r="I13" s="507"/>
+      <c r="J13" s="507"/>
+      <c r="K13" s="508"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="517" t="s">
+      <c r="A14" s="584" t="s">
         <v>326</v>
       </c>
-      <c r="B14" s="518"/>
-      <c r="C14" s="518"/>
-      <c r="D14" s="518"/>
-      <c r="E14" s="518"/>
-      <c r="F14" s="518"/>
-      <c r="G14" s="518"/>
-      <c r="H14" s="518"/>
-      <c r="I14" s="518"/>
-      <c r="J14" s="518"/>
-      <c r="K14" s="519"/>
+      <c r="B14" s="585"/>
+      <c r="C14" s="585"/>
+      <c r="D14" s="585"/>
+      <c r="E14" s="585"/>
+      <c r="F14" s="585"/>
+      <c r="G14" s="585"/>
+      <c r="H14" s="585"/>
+      <c r="I14" s="585"/>
+      <c r="J14" s="585"/>
+      <c r="K14" s="586"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="534" t="s">
+      <c r="A15" s="560" t="s">
         <v>327</v>
       </c>
-      <c r="B15" s="485" t="s">
+      <c r="B15" s="496" t="s">
         <v>328</v>
       </c>
-      <c r="C15" s="538"/>
-      <c r="D15" s="539"/>
-      <c r="E15" s="485" t="s">
+      <c r="C15" s="554"/>
+      <c r="D15" s="555"/>
+      <c r="E15" s="496" t="s">
         <v>329</v>
       </c>
-      <c r="F15" s="486"/>
-      <c r="G15" s="523" t="s">
+      <c r="F15" s="497"/>
+      <c r="G15" s="587" t="s">
         <v>324</v>
       </c>
-      <c r="H15" s="541" t="s">
+      <c r="H15" s="557" t="s">
         <v>330</v>
       </c>
-      <c r="I15" s="514" t="s">
+      <c r="I15" s="495" t="s">
         <v>331</v>
       </c>
-      <c r="J15" s="538"/>
-      <c r="K15" s="551"/>
+      <c r="J15" s="554"/>
+      <c r="K15" s="571"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="534"/>
-      <c r="B16" s="538"/>
-      <c r="C16" s="538"/>
-      <c r="D16" s="539"/>
-      <c r="E16" s="487"/>
-      <c r="F16" s="488"/>
-      <c r="G16" s="523"/>
-      <c r="H16" s="541"/>
-      <c r="I16" s="550"/>
-      <c r="J16" s="538"/>
-      <c r="K16" s="551"/>
+      <c r="A16" s="560"/>
+      <c r="B16" s="554"/>
+      <c r="C16" s="554"/>
+      <c r="D16" s="555"/>
+      <c r="E16" s="477"/>
+      <c r="F16" s="478"/>
+      <c r="G16" s="587"/>
+      <c r="H16" s="557"/>
+      <c r="I16" s="570"/>
+      <c r="J16" s="554"/>
+      <c r="K16" s="571"/>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
-      <c r="B17" s="435"/>
-      <c r="C17" s="435"/>
-      <c r="D17" s="540"/>
+      <c r="B17" s="326"/>
+      <c r="C17" s="326"/>
+      <c r="D17" s="556"/>
       <c r="E17" s="10" t="s">
         <v>129</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="524"/>
-      <c r="H17" s="542"/>
-      <c r="I17" s="552"/>
-      <c r="J17" s="435"/>
-      <c r="K17" s="436"/>
+      <c r="G17" s="588"/>
+      <c r="H17" s="558"/>
+      <c r="I17" s="572"/>
+      <c r="J17" s="326"/>
+      <c r="K17" s="327"/>
     </row>
     <row r="18" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="520"/>
-      <c r="B18" s="521"/>
-      <c r="C18" s="521"/>
-      <c r="D18" s="522"/>
+      <c r="A18" s="523"/>
+      <c r="B18" s="524"/>
+      <c r="C18" s="524"/>
+      <c r="D18" s="525"/>
       <c r="E18" s="256"/>
       <c r="F18" s="256"/>
       <c r="G18" s="257"/>
       <c r="H18" s="258"/>
-      <c r="I18" s="525"/>
-      <c r="J18" s="526"/>
-      <c r="K18" s="527"/>
+      <c r="I18" s="520"/>
+      <c r="J18" s="549"/>
+      <c r="K18" s="550"/>
     </row>
     <row r="19" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="520"/>
-      <c r="B19" s="521"/>
-      <c r="C19" s="521"/>
-      <c r="D19" s="522"/>
+      <c r="A19" s="523"/>
+      <c r="B19" s="524"/>
+      <c r="C19" s="524"/>
+      <c r="D19" s="525"/>
       <c r="E19" s="256"/>
       <c r="F19" s="256"/>
       <c r="G19" s="257"/>
       <c r="H19" s="258"/>
-      <c r="I19" s="525"/>
-      <c r="J19" s="578"/>
-      <c r="K19" s="579"/>
+      <c r="I19" s="520"/>
+      <c r="J19" s="521"/>
+      <c r="K19" s="522"/>
     </row>
     <row r="20" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="520"/>
-      <c r="B20" s="521"/>
-      <c r="C20" s="521"/>
-      <c r="D20" s="522"/>
+      <c r="A20" s="523"/>
+      <c r="B20" s="524"/>
+      <c r="C20" s="524"/>
+      <c r="D20" s="525"/>
       <c r="E20" s="256"/>
       <c r="F20" s="256"/>
       <c r="G20" s="257"/>
       <c r="H20" s="258"/>
-      <c r="I20" s="525"/>
-      <c r="J20" s="578"/>
-      <c r="K20" s="579"/>
+      <c r="I20" s="520"/>
+      <c r="J20" s="521"/>
+      <c r="K20" s="522"/>
     </row>
     <row r="21" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="520"/>
-      <c r="B21" s="521"/>
-      <c r="C21" s="521"/>
-      <c r="D21" s="522"/>
+      <c r="A21" s="523"/>
+      <c r="B21" s="524"/>
+      <c r="C21" s="524"/>
+      <c r="D21" s="525"/>
       <c r="E21" s="256"/>
       <c r="F21" s="256"/>
       <c r="G21" s="257"/>
       <c r="H21" s="258"/>
-      <c r="I21" s="580"/>
-      <c r="J21" s="581"/>
-      <c r="K21" s="582"/>
+      <c r="I21" s="595"/>
+      <c r="J21" s="596"/>
+      <c r="K21" s="597"/>
     </row>
     <row r="22" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="520"/>
-      <c r="B22" s="521"/>
-      <c r="C22" s="521"/>
-      <c r="D22" s="522"/>
+      <c r="A22" s="523"/>
+      <c r="B22" s="524"/>
+      <c r="C22" s="524"/>
+      <c r="D22" s="525"/>
       <c r="E22" s="256"/>
       <c r="F22" s="256"/>
       <c r="G22" s="257"/>
       <c r="H22" s="258"/>
-      <c r="I22" s="525"/>
-      <c r="J22" s="578"/>
-      <c r="K22" s="579"/>
+      <c r="I22" s="520"/>
+      <c r="J22" s="521"/>
+      <c r="K22" s="522"/>
     </row>
     <row r="23" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="520"/>
-      <c r="B23" s="521"/>
-      <c r="C23" s="521"/>
-      <c r="D23" s="522"/>
+      <c r="A23" s="523"/>
+      <c r="B23" s="524"/>
+      <c r="C23" s="524"/>
+      <c r="D23" s="525"/>
       <c r="E23" s="256"/>
       <c r="F23" s="256"/>
       <c r="G23" s="257"/>
       <c r="H23" s="258"/>
-      <c r="I23" s="525"/>
-      <c r="J23" s="578"/>
-      <c r="K23" s="579"/>
+      <c r="I23" s="520"/>
+      <c r="J23" s="521"/>
+      <c r="K23" s="522"/>
     </row>
     <row r="24" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="520"/>
-      <c r="B24" s="521"/>
-      <c r="C24" s="521"/>
-      <c r="D24" s="522"/>
+      <c r="A24" s="523"/>
+      <c r="B24" s="524"/>
+      <c r="C24" s="524"/>
+      <c r="D24" s="525"/>
       <c r="E24" s="256"/>
       <c r="F24" s="256"/>
       <c r="G24" s="257"/>
       <c r="H24" s="258"/>
-      <c r="I24" s="525"/>
-      <c r="J24" s="578"/>
-      <c r="K24" s="579"/>
+      <c r="I24" s="520"/>
+      <c r="J24" s="521"/>
+      <c r="K24" s="522"/>
     </row>
     <row r="25" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="520"/>
-      <c r="B25" s="521"/>
-      <c r="C25" s="521"/>
-      <c r="D25" s="522"/>
+      <c r="A25" s="523"/>
+      <c r="B25" s="524"/>
+      <c r="C25" s="524"/>
+      <c r="D25" s="525"/>
       <c r="E25" s="256"/>
       <c r="F25" s="256"/>
       <c r="G25" s="257"/>
       <c r="H25" s="258"/>
-      <c r="I25" s="525"/>
-      <c r="J25" s="578"/>
-      <c r="K25" s="579"/>
+      <c r="I25" s="520"/>
+      <c r="J25" s="521"/>
+      <c r="K25" s="522"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="520"/>
-      <c r="B26" s="521"/>
-      <c r="C26" s="521"/>
-      <c r="D26" s="522"/>
+      <c r="A26" s="523"/>
+      <c r="B26" s="524"/>
+      <c r="C26" s="524"/>
+      <c r="D26" s="525"/>
       <c r="E26" s="256"/>
       <c r="F26" s="256"/>
       <c r="G26" s="257"/>
       <c r="H26" s="258"/>
-      <c r="I26" s="525"/>
-      <c r="J26" s="526"/>
-      <c r="K26" s="527"/>
+      <c r="I26" s="520"/>
+      <c r="J26" s="549"/>
+      <c r="K26" s="550"/>
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="520"/>
-      <c r="B27" s="521"/>
-      <c r="C27" s="521"/>
-      <c r="D27" s="522"/>
+      <c r="A27" s="523"/>
+      <c r="B27" s="524"/>
+      <c r="C27" s="524"/>
+      <c r="D27" s="525"/>
       <c r="E27" s="256"/>
       <c r="F27" s="256"/>
       <c r="G27" s="257"/>
       <c r="H27" s="258"/>
-      <c r="I27" s="525"/>
-      <c r="J27" s="526"/>
-      <c r="K27" s="527"/>
+      <c r="I27" s="520"/>
+      <c r="J27" s="549"/>
+      <c r="K27" s="550"/>
     </row>
     <row r="28" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="520"/>
-      <c r="B28" s="521"/>
-      <c r="C28" s="521"/>
-      <c r="D28" s="522"/>
+      <c r="A28" s="523"/>
+      <c r="B28" s="524"/>
+      <c r="C28" s="524"/>
+      <c r="D28" s="525"/>
       <c r="E28" s="256"/>
       <c r="F28" s="256"/>
       <c r="G28" s="257"/>
       <c r="H28" s="258"/>
-      <c r="I28" s="525"/>
-      <c r="J28" s="526"/>
-      <c r="K28" s="527"/>
+      <c r="I28" s="520"/>
+      <c r="J28" s="549"/>
+      <c r="K28" s="550"/>
     </row>
     <row r="29" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="520"/>
-      <c r="B29" s="521"/>
-      <c r="C29" s="521"/>
-      <c r="D29" s="522"/>
+      <c r="A29" s="523"/>
+      <c r="B29" s="524"/>
+      <c r="C29" s="524"/>
+      <c r="D29" s="525"/>
       <c r="E29" s="256"/>
       <c r="F29" s="256"/>
       <c r="G29" s="257"/>
       <c r="H29" s="258"/>
-      <c r="I29" s="525"/>
-      <c r="J29" s="578"/>
-      <c r="K29" s="579"/>
+      <c r="I29" s="520"/>
+      <c r="J29" s="521"/>
+      <c r="K29" s="522"/>
     </row>
     <row r="30" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="520"/>
-      <c r="B30" s="521"/>
-      <c r="C30" s="521"/>
-      <c r="D30" s="522"/>
+      <c r="A30" s="523"/>
+      <c r="B30" s="524"/>
+      <c r="C30" s="524"/>
+      <c r="D30" s="525"/>
       <c r="E30" s="256"/>
       <c r="F30" s="256"/>
       <c r="G30" s="257"/>
       <c r="H30" s="258"/>
-      <c r="I30" s="525"/>
-      <c r="J30" s="578"/>
-      <c r="K30" s="579"/>
+      <c r="I30" s="520"/>
+      <c r="J30" s="521"/>
+      <c r="K30" s="522"/>
     </row>
     <row r="31" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="520"/>
-      <c r="B31" s="521"/>
-      <c r="C31" s="521"/>
-      <c r="D31" s="522"/>
+      <c r="A31" s="523"/>
+      <c r="B31" s="524"/>
+      <c r="C31" s="524"/>
+      <c r="D31" s="525"/>
       <c r="E31" s="256"/>
       <c r="F31" s="256"/>
       <c r="G31" s="257"/>
       <c r="H31" s="258"/>
-      <c r="I31" s="525"/>
-      <c r="J31" s="578"/>
-      <c r="K31" s="579"/>
+      <c r="I31" s="520"/>
+      <c r="J31" s="521"/>
+      <c r="K31" s="522"/>
     </row>
     <row r="32" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="520"/>
-      <c r="B32" s="521"/>
-      <c r="C32" s="521"/>
-      <c r="D32" s="522"/>
+      <c r="A32" s="523"/>
+      <c r="B32" s="524"/>
+      <c r="C32" s="524"/>
+      <c r="D32" s="525"/>
       <c r="E32" s="256"/>
       <c r="F32" s="256"/>
       <c r="G32" s="257"/>
       <c r="H32" s="258"/>
-      <c r="I32" s="525"/>
-      <c r="J32" s="578"/>
-      <c r="K32" s="579"/>
+      <c r="I32" s="520"/>
+      <c r="J32" s="521"/>
+      <c r="K32" s="522"/>
     </row>
     <row r="33" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="520"/>
-      <c r="B33" s="521"/>
-      <c r="C33" s="521"/>
-      <c r="D33" s="522"/>
+      <c r="A33" s="523"/>
+      <c r="B33" s="524"/>
+      <c r="C33" s="524"/>
+      <c r="D33" s="525"/>
       <c r="E33" s="256"/>
       <c r="F33" s="256"/>
       <c r="G33" s="257"/>
       <c r="H33" s="258"/>
-      <c r="I33" s="525"/>
-      <c r="J33" s="578"/>
-      <c r="K33" s="579"/>
+      <c r="I33" s="520"/>
+      <c r="J33" s="521"/>
+      <c r="K33" s="522"/>
     </row>
     <row r="34" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="520"/>
-      <c r="B34" s="521"/>
-      <c r="C34" s="521"/>
-      <c r="D34" s="522"/>
+      <c r="A34" s="523"/>
+      <c r="B34" s="524"/>
+      <c r="C34" s="524"/>
+      <c r="D34" s="525"/>
       <c r="E34" s="256"/>
       <c r="F34" s="256"/>
       <c r="G34" s="257"/>
       <c r="H34" s="258"/>
-      <c r="I34" s="525"/>
-      <c r="J34" s="578"/>
-      <c r="K34" s="579"/>
+      <c r="I34" s="520"/>
+      <c r="J34" s="521"/>
+      <c r="K34" s="522"/>
     </row>
     <row r="35" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="520"/>
-      <c r="B35" s="521"/>
-      <c r="C35" s="521"/>
-      <c r="D35" s="522"/>
+      <c r="A35" s="523"/>
+      <c r="B35" s="524"/>
+      <c r="C35" s="524"/>
+      <c r="D35" s="525"/>
       <c r="E35" s="256"/>
       <c r="F35" s="256"/>
       <c r="G35" s="257"/>
       <c r="H35" s="258"/>
-      <c r="I35" s="525"/>
-      <c r="J35" s="526"/>
-      <c r="K35" s="527"/>
+      <c r="I35" s="520"/>
+      <c r="J35" s="549"/>
+      <c r="K35" s="550"/>
     </row>
     <row r="36" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="520"/>
-      <c r="B36" s="521"/>
-      <c r="C36" s="521"/>
-      <c r="D36" s="522"/>
+      <c r="A36" s="523"/>
+      <c r="B36" s="524"/>
+      <c r="C36" s="524"/>
+      <c r="D36" s="525"/>
       <c r="E36" s="256"/>
       <c r="F36" s="256"/>
       <c r="G36" s="257"/>
       <c r="H36" s="258"/>
-      <c r="I36" s="525"/>
-      <c r="J36" s="526"/>
-      <c r="K36" s="527"/>
+      <c r="I36" s="520"/>
+      <c r="J36" s="549"/>
+      <c r="K36" s="550"/>
     </row>
     <row r="37" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="520"/>
-      <c r="B37" s="521"/>
-      <c r="C37" s="521"/>
-      <c r="D37" s="522"/>
+      <c r="A37" s="523"/>
+      <c r="B37" s="524"/>
+      <c r="C37" s="524"/>
+      <c r="D37" s="525"/>
       <c r="E37" s="256"/>
       <c r="F37" s="256"/>
       <c r="G37" s="257"/>
       <c r="H37" s="258"/>
-      <c r="I37" s="525"/>
-      <c r="J37" s="526"/>
-      <c r="K37" s="527"/>
+      <c r="I37" s="520"/>
+      <c r="J37" s="549"/>
+      <c r="K37" s="550"/>
     </row>
     <row r="38" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="528"/>
-      <c r="B38" s="529"/>
-      <c r="C38" s="529"/>
-      <c r="D38" s="530"/>
+      <c r="A38" s="589"/>
+      <c r="B38" s="590"/>
+      <c r="C38" s="590"/>
+      <c r="D38" s="591"/>
       <c r="E38" s="256"/>
       <c r="F38" s="256"/>
       <c r="G38" s="259"/>
       <c r="H38" s="260"/>
-      <c r="I38" s="531"/>
-      <c r="J38" s="532"/>
-      <c r="K38" s="533"/>
+      <c r="I38" s="592"/>
+      <c r="J38" s="593"/>
+      <c r="K38" s="594"/>
     </row>
     <row r="39" spans="1:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="450" t="s">
+      <c r="A39" s="274" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="451"/>
-      <c r="C39" s="451"/>
-      <c r="D39" s="451"/>
-      <c r="E39" s="451"/>
-      <c r="F39" s="451"/>
-      <c r="G39" s="451"/>
-      <c r="H39" s="451"/>
-      <c r="I39" s="451"/>
-      <c r="J39" s="451"/>
-      <c r="K39" s="452"/>
+      <c r="B39" s="275"/>
+      <c r="C39" s="275"/>
+      <c r="D39" s="275"/>
+      <c r="E39" s="275"/>
+      <c r="F39" s="275"/>
+      <c r="G39" s="275"/>
+      <c r="H39" s="275"/>
+      <c r="I39" s="275"/>
+      <c r="J39" s="275"/>
+      <c r="K39" s="276"/>
     </row>
     <row r="40" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="568" t="s">
+      <c r="A40" s="526" t="s">
         <v>332</v>
       </c>
-      <c r="B40" s="569"/>
-      <c r="C40" s="569"/>
-      <c r="D40" s="569"/>
-      <c r="E40" s="569"/>
-      <c r="F40" s="569"/>
-      <c r="G40" s="569"/>
-      <c r="H40" s="569"/>
-      <c r="I40" s="569"/>
-      <c r="J40" s="569"/>
-      <c r="K40" s="570"/>
+      <c r="B40" s="527"/>
+      <c r="C40" s="527"/>
+      <c r="D40" s="527"/>
+      <c r="E40" s="527"/>
+      <c r="F40" s="527"/>
+      <c r="G40" s="527"/>
+      <c r="H40" s="527"/>
+      <c r="I40" s="527"/>
+      <c r="J40" s="527"/>
+      <c r="K40" s="528"/>
     </row>
     <row r="41" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="117" t="s">
@@ -17183,145 +17183,145 @@
       <c r="C41" s="118" t="s">
         <v>335</v>
       </c>
-      <c r="D41" s="561" t="s">
+      <c r="D41" s="544" t="s">
         <v>336</v>
       </c>
-      <c r="E41" s="561"/>
-      <c r="F41" s="561"/>
-      <c r="G41" s="561"/>
-      <c r="H41" s="562"/>
+      <c r="E41" s="544"/>
+      <c r="F41" s="544"/>
+      <c r="G41" s="544"/>
+      <c r="H41" s="545"/>
       <c r="I41" s="118" t="s">
         <v>337</v>
       </c>
-      <c r="J41" s="561" t="s">
+      <c r="J41" s="544" t="s">
         <v>338</v>
       </c>
-      <c r="K41" s="387"/>
+      <c r="K41" s="358"/>
     </row>
     <row r="42" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="566"/>
-      <c r="B42" s="567"/>
-      <c r="C42" s="563"/>
-      <c r="D42" s="564"/>
-      <c r="E42" s="564"/>
-      <c r="F42" s="564"/>
-      <c r="G42" s="564"/>
-      <c r="H42" s="567"/>
-      <c r="I42" s="563"/>
-      <c r="J42" s="564"/>
-      <c r="K42" s="565"/>
+      <c r="A42" s="536"/>
+      <c r="B42" s="537"/>
+      <c r="C42" s="538"/>
+      <c r="D42" s="539"/>
+      <c r="E42" s="539"/>
+      <c r="F42" s="539"/>
+      <c r="G42" s="539"/>
+      <c r="H42" s="537"/>
+      <c r="I42" s="538"/>
+      <c r="J42" s="539"/>
+      <c r="K42" s="540"/>
     </row>
     <row r="43" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="566"/>
-      <c r="B43" s="567"/>
-      <c r="C43" s="563"/>
-      <c r="D43" s="564"/>
-      <c r="E43" s="564"/>
-      <c r="F43" s="564"/>
-      <c r="G43" s="564"/>
-      <c r="H43" s="567"/>
-      <c r="I43" s="563"/>
-      <c r="J43" s="564"/>
-      <c r="K43" s="565"/>
+      <c r="A43" s="536"/>
+      <c r="B43" s="537"/>
+      <c r="C43" s="538"/>
+      <c r="D43" s="539"/>
+      <c r="E43" s="539"/>
+      <c r="F43" s="539"/>
+      <c r="G43" s="539"/>
+      <c r="H43" s="537"/>
+      <c r="I43" s="538"/>
+      <c r="J43" s="539"/>
+      <c r="K43" s="540"/>
     </row>
     <row r="44" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="566"/>
-      <c r="B44" s="567"/>
-      <c r="C44" s="563"/>
-      <c r="D44" s="564"/>
-      <c r="E44" s="564"/>
-      <c r="F44" s="564"/>
-      <c r="G44" s="564"/>
-      <c r="H44" s="567"/>
-      <c r="I44" s="563"/>
-      <c r="J44" s="564"/>
-      <c r="K44" s="565"/>
+      <c r="A44" s="536"/>
+      <c r="B44" s="537"/>
+      <c r="C44" s="538"/>
+      <c r="D44" s="539"/>
+      <c r="E44" s="539"/>
+      <c r="F44" s="539"/>
+      <c r="G44" s="539"/>
+      <c r="H44" s="537"/>
+      <c r="I44" s="538"/>
+      <c r="J44" s="539"/>
+      <c r="K44" s="540"/>
     </row>
     <row r="45" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="566"/>
-      <c r="B45" s="567"/>
-      <c r="C45" s="563"/>
-      <c r="D45" s="564"/>
-      <c r="E45" s="564"/>
-      <c r="F45" s="564"/>
-      <c r="G45" s="564"/>
-      <c r="H45" s="567"/>
-      <c r="I45" s="563"/>
-      <c r="J45" s="564"/>
-      <c r="K45" s="565"/>
+      <c r="A45" s="536"/>
+      <c r="B45" s="537"/>
+      <c r="C45" s="538"/>
+      <c r="D45" s="539"/>
+      <c r="E45" s="539"/>
+      <c r="F45" s="539"/>
+      <c r="G45" s="539"/>
+      <c r="H45" s="537"/>
+      <c r="I45" s="538"/>
+      <c r="J45" s="539"/>
+      <c r="K45" s="540"/>
     </row>
     <row r="46" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="566"/>
-      <c r="B46" s="567"/>
-      <c r="C46" s="563"/>
-      <c r="D46" s="564"/>
-      <c r="E46" s="564"/>
-      <c r="F46" s="564"/>
-      <c r="G46" s="564"/>
-      <c r="H46" s="567"/>
-      <c r="I46" s="563"/>
-      <c r="J46" s="564"/>
-      <c r="K46" s="565"/>
+      <c r="A46" s="536"/>
+      <c r="B46" s="537"/>
+      <c r="C46" s="538"/>
+      <c r="D46" s="539"/>
+      <c r="E46" s="539"/>
+      <c r="F46" s="539"/>
+      <c r="G46" s="539"/>
+      <c r="H46" s="537"/>
+      <c r="I46" s="538"/>
+      <c r="J46" s="539"/>
+      <c r="K46" s="540"/>
     </row>
     <row r="47" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="566"/>
-      <c r="B47" s="567"/>
-      <c r="C47" s="563"/>
-      <c r="D47" s="564"/>
-      <c r="E47" s="564"/>
-      <c r="F47" s="564"/>
-      <c r="G47" s="564"/>
-      <c r="H47" s="567"/>
-      <c r="I47" s="563"/>
-      <c r="J47" s="564"/>
-      <c r="K47" s="565"/>
+      <c r="A47" s="536"/>
+      <c r="B47" s="537"/>
+      <c r="C47" s="538"/>
+      <c r="D47" s="539"/>
+      <c r="E47" s="539"/>
+      <c r="F47" s="539"/>
+      <c r="G47" s="539"/>
+      <c r="H47" s="537"/>
+      <c r="I47" s="538"/>
+      <c r="J47" s="539"/>
+      <c r="K47" s="540"/>
     </row>
     <row r="48" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="566"/>
-      <c r="B48" s="567"/>
-      <c r="C48" s="563"/>
-      <c r="D48" s="564"/>
-      <c r="E48" s="564"/>
-      <c r="F48" s="564"/>
-      <c r="G48" s="564"/>
-      <c r="H48" s="567"/>
-      <c r="I48" s="563"/>
-      <c r="J48" s="564"/>
-      <c r="K48" s="565"/>
+      <c r="A48" s="536"/>
+      <c r="B48" s="537"/>
+      <c r="C48" s="538"/>
+      <c r="D48" s="539"/>
+      <c r="E48" s="539"/>
+      <c r="F48" s="539"/>
+      <c r="G48" s="539"/>
+      <c r="H48" s="537"/>
+      <c r="I48" s="538"/>
+      <c r="J48" s="539"/>
+      <c r="K48" s="540"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="450" t="s">
+      <c r="A49" s="274" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="451"/>
-      <c r="C49" s="451"/>
-      <c r="D49" s="451"/>
-      <c r="E49" s="451"/>
-      <c r="F49" s="451"/>
-      <c r="G49" s="451"/>
-      <c r="H49" s="451"/>
-      <c r="I49" s="451"/>
-      <c r="J49" s="451"/>
-      <c r="K49" s="491"/>
+      <c r="B49" s="275"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="275"/>
+      <c r="G49" s="275"/>
+      <c r="H49" s="275"/>
+      <c r="I49" s="275"/>
+      <c r="J49" s="275"/>
+      <c r="K49" s="508"/>
     </row>
     <row r="50" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="447" t="s">
+      <c r="A50" s="271" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="449"/>
-      <c r="C50" s="481" t="s">
+      <c r="B50" s="273"/>
+      <c r="C50" s="500" t="s">
         <v>144</v>
       </c>
-      <c r="D50" s="573"/>
-      <c r="E50" s="573"/>
-      <c r="F50" s="574"/>
-      <c r="G50" s="571" t="s">
+      <c r="D50" s="531"/>
+      <c r="E50" s="531"/>
+      <c r="F50" s="532"/>
+      <c r="G50" s="529" t="s">
         <v>145</v>
       </c>
-      <c r="H50" s="572"/>
-      <c r="I50" s="575"/>
-      <c r="J50" s="576"/>
-      <c r="K50" s="577"/>
+      <c r="H50" s="530"/>
+      <c r="I50" s="533"/>
+      <c r="J50" s="534"/>
+      <c r="K50" s="535"/>
       <c r="L50" s="216"/>
       <c r="M50" s="216"/>
     </row>
@@ -17342,36 +17342,54 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="102">
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="C48:H48"/>
-    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B15:D17"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="H3:K5"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I15:K17"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="H8:K8"/>
     <mergeCell ref="D41:H41"/>
     <mergeCell ref="I43:K43"/>
@@ -17396,54 +17414,36 @@
     <mergeCell ref="I35:K35"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="I36:K36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B15:D17"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="H3:K5"/>
-    <mergeCell ref="E3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I15:K17"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="C48:H48"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -17476,35 +17476,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="590"/>
-      <c r="B1" s="591"/>
-      <c r="C1" s="591"/>
-      <c r="D1" s="591"/>
-      <c r="E1" s="591"/>
-      <c r="F1" s="591"/>
-      <c r="G1" s="591"/>
-      <c r="H1" s="591"/>
-      <c r="I1" s="591"/>
-      <c r="J1" s="591"/>
-      <c r="K1" s="591"/>
-      <c r="L1" s="591"/>
-      <c r="M1" s="592"/>
+      <c r="A1" s="714"/>
+      <c r="B1" s="715"/>
+      <c r="C1" s="715"/>
+      <c r="D1" s="715"/>
+      <c r="E1" s="715"/>
+      <c r="F1" s="715"/>
+      <c r="G1" s="715"/>
+      <c r="H1" s="715"/>
+      <c r="I1" s="715"/>
+      <c r="J1" s="715"/>
+      <c r="K1" s="715"/>
+      <c r="L1" s="715"/>
+      <c r="M1" s="716"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="615" t="s">
+      <c r="A2" s="691" t="s">
         <v>339</v>
       </c>
-      <c r="B2" s="616"/>
-      <c r="C2" s="595" t="s">
+      <c r="B2" s="692"/>
+      <c r="C2" s="719" t="s">
         <v>340</v>
       </c>
-      <c r="D2" s="595"/>
-      <c r="E2" s="595"/>
-      <c r="F2" s="596"/>
+      <c r="D2" s="719"/>
+      <c r="E2" s="719"/>
+      <c r="F2" s="720"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
-      <c r="I2" s="593"/>
-      <c r="J2" s="593"/>
+      <c r="I2" s="717"/>
+      <c r="J2" s="717"/>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
       <c r="M2" s="13"/>
@@ -17512,16 +17512,16 @@
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14"/>
       <c r="B3" s="15"/>
-      <c r="C3" s="599" t="s">
+      <c r="C3" s="707" t="s">
         <v>341</v>
       </c>
-      <c r="D3" s="599"/>
-      <c r="E3" s="599"/>
-      <c r="F3" s="600"/>
+      <c r="D3" s="707"/>
+      <c r="E3" s="707"/>
+      <c r="F3" s="708"/>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
-      <c r="I3" s="594"/>
-      <c r="J3" s="594"/>
+      <c r="I3" s="718"/>
+      <c r="J3" s="718"/>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
       <c r="M3" s="18"/>
@@ -17529,42 +17529,42 @@
     <row r="4" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="599" t="s">
+      <c r="C4" s="707" t="s">
         <v>342</v>
       </c>
-      <c r="D4" s="599"/>
-      <c r="E4" s="599"/>
-      <c r="F4" s="600"/>
+      <c r="D4" s="707"/>
+      <c r="E4" s="707"/>
+      <c r="F4" s="708"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14"/>
       <c r="B5" s="15"/>
-      <c r="C5" s="599"/>
-      <c r="D5" s="599"/>
-      <c r="E5" s="599"/>
-      <c r="F5" s="600"/>
-      <c r="G5" s="587"/>
-      <c r="H5" s="587"/>
-      <c r="I5" s="587"/>
-      <c r="J5" s="587"/>
-      <c r="K5" s="587"/>
-      <c r="L5" s="587"/>
+      <c r="C5" s="707"/>
+      <c r="D5" s="707"/>
+      <c r="E5" s="707"/>
+      <c r="F5" s="708"/>
+      <c r="G5" s="623"/>
+      <c r="H5" s="623"/>
+      <c r="I5" s="623"/>
+      <c r="J5" s="623"/>
+      <c r="K5" s="623"/>
+      <c r="L5" s="623"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="15"/>
-      <c r="C6" s="599" t="s">
+      <c r="C6" s="707" t="s">
         <v>343</v>
       </c>
-      <c r="D6" s="599"/>
-      <c r="E6" s="599"/>
-      <c r="F6" s="600"/>
-      <c r="I6" s="621"/>
-      <c r="J6" s="621"/>
-      <c r="K6" s="621"/>
-      <c r="L6" s="621"/>
+      <c r="D6" s="707"/>
+      <c r="E6" s="707"/>
+      <c r="F6" s="708"/>
+      <c r="I6" s="713"/>
+      <c r="J6" s="713"/>
+      <c r="K6" s="713"/>
+      <c r="L6" s="713"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -17583,12 +17583,12 @@
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="15"/>
-      <c r="C8" s="599" t="s">
+      <c r="C8" s="707" t="s">
         <v>344</v>
       </c>
-      <c r="D8" s="599"/>
-      <c r="E8" s="599"/>
-      <c r="F8" s="600"/>
+      <c r="D8" s="707"/>
+      <c r="E8" s="707"/>
+      <c r="F8" s="708"/>
       <c r="M8" s="19"/>
     </row>
     <row r="9" spans="1:13" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -17603,61 +17603,61 @@
     <row r="10" spans="1:13" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="15"/>
-      <c r="C10" s="599"/>
-      <c r="D10" s="599"/>
-      <c r="E10" s="599"/>
-      <c r="F10" s="600"/>
-      <c r="G10" s="587" t="s">
+      <c r="C10" s="707"/>
+      <c r="D10" s="707"/>
+      <c r="E10" s="707"/>
+      <c r="F10" s="708"/>
+      <c r="G10" s="623" t="s">
         <v>345</v>
       </c>
-      <c r="H10" s="587"/>
-      <c r="I10" s="587"/>
-      <c r="J10" s="587"/>
-      <c r="K10" s="587"/>
-      <c r="L10" s="587"/>
+      <c r="H10" s="623"/>
+      <c r="I10" s="623"/>
+      <c r="J10" s="623"/>
+      <c r="K10" s="623"/>
+      <c r="L10" s="623"/>
       <c r="M10" s="66"/>
     </row>
     <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="15"/>
-      <c r="C11" s="599"/>
-      <c r="D11" s="599"/>
-      <c r="E11" s="599"/>
-      <c r="F11" s="600"/>
+      <c r="C11" s="707"/>
+      <c r="D11" s="707"/>
+      <c r="E11" s="707"/>
+      <c r="F11" s="708"/>
       <c r="G11" s="125"/>
       <c r="H11" s="126"/>
-      <c r="I11" s="619"/>
-      <c r="J11" s="619"/>
-      <c r="K11" s="619"/>
-      <c r="L11" s="619"/>
+      <c r="I11" s="711"/>
+      <c r="J11" s="711"/>
+      <c r="K11" s="711"/>
+      <c r="L11" s="711"/>
       <c r="M11" s="66"/>
     </row>
     <row r="12" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="617"/>
-      <c r="D12" s="617"/>
-      <c r="E12" s="617"/>
-      <c r="F12" s="618"/>
+      <c r="C12" s="709"/>
+      <c r="D12" s="709"/>
+      <c r="E12" s="709"/>
+      <c r="F12" s="710"/>
       <c r="G12" s="126"/>
       <c r="H12" s="126"/>
-      <c r="I12" s="620"/>
-      <c r="J12" s="620"/>
-      <c r="K12" s="620"/>
-      <c r="L12" s="620"/>
+      <c r="I12" s="712"/>
+      <c r="J12" s="712"/>
+      <c r="K12" s="712"/>
+      <c r="L12" s="712"/>
       <c r="M12" s="104"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="583" t="s">
+      <c r="A13" s="731" t="s">
         <v>346</v>
       </c>
-      <c r="B13" s="584"/>
-      <c r="C13" s="585" t="s">
+      <c r="B13" s="732"/>
+      <c r="C13" s="727" t="s">
         <v>347</v>
       </c>
-      <c r="D13" s="585"/>
-      <c r="E13" s="538"/>
-      <c r="F13" s="539"/>
+      <c r="D13" s="727"/>
+      <c r="E13" s="554"/>
+      <c r="F13" s="555"/>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
       <c r="I13" s="22"/>
@@ -17669,48 +17669,48 @@
     <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
       <c r="B14" s="38"/>
-      <c r="C14" s="585"/>
-      <c r="D14" s="585"/>
-      <c r="E14" s="538"/>
-      <c r="F14" s="539"/>
-      <c r="G14" s="586" t="s">
+      <c r="C14" s="727"/>
+      <c r="D14" s="727"/>
+      <c r="E14" s="554"/>
+      <c r="F14" s="555"/>
+      <c r="G14" s="622" t="s">
         <v>345</v>
       </c>
-      <c r="H14" s="587"/>
-      <c r="I14" s="587"/>
-      <c r="J14" s="587"/>
-      <c r="K14" s="587"/>
-      <c r="L14" s="587"/>
+      <c r="H14" s="623"/>
+      <c r="I14" s="623"/>
+      <c r="J14" s="623"/>
+      <c r="K14" s="623"/>
+      <c r="L14" s="623"/>
       <c r="M14" s="103"/>
     </row>
     <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
       <c r="B15" s="38"/>
-      <c r="C15" s="585"/>
-      <c r="D15" s="585"/>
-      <c r="E15" s="538"/>
-      <c r="F15" s="539"/>
+      <c r="C15" s="727"/>
+      <c r="D15" s="727"/>
+      <c r="E15" s="554"/>
+      <c r="F15" s="555"/>
       <c r="G15" s="16"/>
       <c r="H15" s="231"/>
-      <c r="I15" s="588"/>
-      <c r="J15" s="588"/>
-      <c r="K15" s="588"/>
-      <c r="L15" s="588"/>
+      <c r="I15" s="733"/>
+      <c r="J15" s="733"/>
+      <c r="K15" s="733"/>
+      <c r="L15" s="733"/>
       <c r="M15" s="103"/>
     </row>
     <row r="16" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
       <c r="B16" s="25"/>
-      <c r="C16" s="538"/>
-      <c r="D16" s="538"/>
-      <c r="E16" s="538"/>
-      <c r="F16" s="539"/>
+      <c r="C16" s="554"/>
+      <c r="D16" s="554"/>
+      <c r="E16" s="554"/>
+      <c r="F16" s="555"/>
       <c r="G16" s="100"/>
       <c r="H16" s="221"/>
-      <c r="I16" s="589"/>
-      <c r="J16" s="589"/>
-      <c r="K16" s="589"/>
-      <c r="L16" s="589"/>
+      <c r="I16" s="724"/>
+      <c r="J16" s="724"/>
+      <c r="K16" s="724"/>
+      <c r="L16" s="724"/>
       <c r="M16" s="101"/>
     </row>
     <row r="17" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17731,12 +17731,12 @@
     <row r="18" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="26"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="713" t="s">
+      <c r="C18" s="625" t="s">
         <v>348</v>
       </c>
-      <c r="D18" s="713"/>
-      <c r="E18" s="714"/>
-      <c r="F18" s="715"/>
+      <c r="D18" s="625"/>
+      <c r="E18" s="626"/>
+      <c r="F18" s="627"/>
       <c r="G18" s="31"/>
       <c r="H18" s="31"/>
       <c r="I18" s="31"/>
@@ -17748,32 +17748,32 @@
     <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="26"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="713"/>
-      <c r="D19" s="713"/>
-      <c r="E19" s="714"/>
-      <c r="F19" s="715"/>
-      <c r="G19" s="586" t="s">
+      <c r="C19" s="625"/>
+      <c r="D19" s="625"/>
+      <c r="E19" s="626"/>
+      <c r="F19" s="627"/>
+      <c r="G19" s="622" t="s">
         <v>345</v>
       </c>
-      <c r="H19" s="587"/>
-      <c r="I19" s="587"/>
-      <c r="J19" s="587"/>
-      <c r="K19" s="587"/>
-      <c r="L19" s="587"/>
+      <c r="H19" s="623"/>
+      <c r="I19" s="623"/>
+      <c r="J19" s="623"/>
+      <c r="K19" s="623"/>
+      <c r="L19" s="623"/>
       <c r="M19" s="32"/>
     </row>
     <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="26"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="713"/>
-      <c r="D20" s="713"/>
-      <c r="E20" s="714"/>
-      <c r="F20" s="715"/>
+      <c r="C20" s="625"/>
+      <c r="D20" s="625"/>
+      <c r="E20" s="626"/>
+      <c r="F20" s="627"/>
       <c r="G20" s="31"/>
-      <c r="H20" s="691" t="s">
+      <c r="H20" s="598" t="s">
         <v>349</v>
       </c>
-      <c r="I20" s="691"/>
+      <c r="I20" s="598"/>
       <c r="J20" s="232"/>
       <c r="K20" s="233"/>
       <c r="L20" s="105"/>
@@ -17782,15 +17782,15 @@
     <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="26"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="713"/>
-      <c r="D21" s="713"/>
-      <c r="E21" s="714"/>
-      <c r="F21" s="715"/>
-      <c r="G21" s="692" t="s">
+      <c r="C21" s="625"/>
+      <c r="D21" s="625"/>
+      <c r="E21" s="626"/>
+      <c r="F21" s="627"/>
+      <c r="G21" s="599" t="s">
         <v>350</v>
       </c>
-      <c r="H21" s="693"/>
-      <c r="I21" s="693"/>
+      <c r="H21" s="600"/>
+      <c r="I21" s="600"/>
       <c r="J21" s="232"/>
       <c r="K21" s="234"/>
       <c r="L21" s="105"/>
@@ -17799,31 +17799,31 @@
     <row r="22" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33"/>
       <c r="B22" s="34"/>
-      <c r="C22" s="716"/>
-      <c r="D22" s="716"/>
-      <c r="E22" s="716"/>
-      <c r="F22" s="717"/>
+      <c r="C22" s="628"/>
+      <c r="D22" s="628"/>
+      <c r="E22" s="628"/>
+      <c r="F22" s="629"/>
       <c r="G22" s="100" t="s">
         <v>351</v>
       </c>
       <c r="H22" s="221"/>
-      <c r="I22" s="718"/>
-      <c r="J22" s="718"/>
-      <c r="K22" s="718"/>
+      <c r="I22" s="630"/>
+      <c r="J22" s="630"/>
+      <c r="K22" s="630"/>
       <c r="L22" s="106"/>
       <c r="M22" s="101"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="622" t="s">
+      <c r="A23" s="618" t="s">
         <v>352</v>
       </c>
-      <c r="B23" s="623"/>
-      <c r="C23" s="611" t="s">
+      <c r="B23" s="619"/>
+      <c r="C23" s="632" t="s">
         <v>353</v>
       </c>
-      <c r="D23" s="611"/>
-      <c r="E23" s="611"/>
-      <c r="F23" s="612"/>
+      <c r="D23" s="632"/>
+      <c r="E23" s="632"/>
+      <c r="F23" s="633"/>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
       <c r="I23" s="22"/>
@@ -17835,61 +17835,61 @@
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="24"/>
       <c r="B24" s="25"/>
-      <c r="C24" s="602"/>
-      <c r="D24" s="602"/>
-      <c r="E24" s="602"/>
-      <c r="F24" s="601"/>
-      <c r="G24" s="586" t="s">
+      <c r="C24" s="634"/>
+      <c r="D24" s="634"/>
+      <c r="E24" s="634"/>
+      <c r="F24" s="635"/>
+      <c r="G24" s="622" t="s">
         <v>345</v>
       </c>
-      <c r="H24" s="587"/>
-      <c r="I24" s="587"/>
-      <c r="J24" s="587"/>
-      <c r="K24" s="587"/>
-      <c r="L24" s="587"/>
+      <c r="H24" s="623"/>
+      <c r="I24" s="623"/>
+      <c r="J24" s="623"/>
+      <c r="K24" s="623"/>
+      <c r="L24" s="623"/>
       <c r="M24" s="99"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
       <c r="B25" s="25"/>
-      <c r="C25" s="602"/>
-      <c r="D25" s="602"/>
-      <c r="E25" s="602"/>
-      <c r="F25" s="601"/>
+      <c r="C25" s="634"/>
+      <c r="D25" s="634"/>
+      <c r="E25" s="634"/>
+      <c r="F25" s="635"/>
       <c r="G25" s="98"/>
       <c r="H25" s="221"/>
-      <c r="I25" s="610"/>
-      <c r="J25" s="610"/>
-      <c r="K25" s="610"/>
-      <c r="L25" s="610"/>
+      <c r="I25" s="631"/>
+      <c r="J25" s="631"/>
+      <c r="K25" s="631"/>
+      <c r="L25" s="631"/>
       <c r="M25" s="99"/>
     </row>
     <row r="26" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="35"/>
       <c r="B26" s="36"/>
-      <c r="C26" s="613"/>
-      <c r="D26" s="613"/>
-      <c r="E26" s="613"/>
-      <c r="F26" s="614"/>
+      <c r="C26" s="636"/>
+      <c r="D26" s="636"/>
+      <c r="E26" s="636"/>
+      <c r="F26" s="637"/>
       <c r="G26" s="100"/>
       <c r="H26" s="221"/>
-      <c r="I26" s="589"/>
-      <c r="J26" s="589"/>
-      <c r="K26" s="589"/>
-      <c r="L26" s="589"/>
+      <c r="I26" s="724"/>
+      <c r="J26" s="724"/>
+      <c r="K26" s="724"/>
+      <c r="L26" s="724"/>
       <c r="M26" s="101"/>
     </row>
     <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="622" t="s">
+      <c r="A27" s="618" t="s">
         <v>354</v>
       </c>
-      <c r="B27" s="623"/>
-      <c r="C27" s="611" t="s">
+      <c r="B27" s="619"/>
+      <c r="C27" s="632" t="s">
         <v>355</v>
       </c>
-      <c r="D27" s="611"/>
-      <c r="E27" s="611"/>
-      <c r="F27" s="612"/>
+      <c r="D27" s="632"/>
+      <c r="E27" s="632"/>
+      <c r="F27" s="633"/>
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="I27" s="22"/>
@@ -17901,41 +17901,41 @@
     <row r="28" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
       <c r="B28" s="25"/>
-      <c r="C28" s="602"/>
-      <c r="D28" s="602"/>
-      <c r="E28" s="602"/>
-      <c r="F28" s="601"/>
-      <c r="G28" s="586" t="s">
+      <c r="C28" s="634"/>
+      <c r="D28" s="634"/>
+      <c r="E28" s="634"/>
+      <c r="F28" s="635"/>
+      <c r="G28" s="622" t="s">
         <v>345</v>
       </c>
-      <c r="H28" s="587"/>
-      <c r="I28" s="587"/>
-      <c r="J28" s="587"/>
-      <c r="K28" s="587"/>
-      <c r="L28" s="587"/>
+      <c r="H28" s="623"/>
+      <c r="I28" s="623"/>
+      <c r="J28" s="623"/>
+      <c r="K28" s="623"/>
+      <c r="L28" s="623"/>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
       <c r="B29" s="25"/>
-      <c r="C29" s="602"/>
-      <c r="D29" s="602"/>
-      <c r="E29" s="602"/>
-      <c r="F29" s="601"/>
+      <c r="C29" s="634"/>
+      <c r="D29" s="634"/>
+      <c r="E29" s="634"/>
+      <c r="F29" s="635"/>
       <c r="H29" s="157"/>
-      <c r="I29" s="610"/>
-      <c r="J29" s="610"/>
-      <c r="K29" s="610"/>
-      <c r="L29" s="610"/>
+      <c r="I29" s="631"/>
+      <c r="J29" s="631"/>
+      <c r="K29" s="631"/>
+      <c r="L29" s="631"/>
       <c r="M29" s="99"/>
     </row>
     <row r="30" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="35"/>
       <c r="B30" s="36"/>
-      <c r="C30" s="613"/>
-      <c r="D30" s="613"/>
-      <c r="E30" s="613"/>
-      <c r="F30" s="614"/>
+      <c r="C30" s="636"/>
+      <c r="D30" s="636"/>
+      <c r="E30" s="636"/>
+      <c r="F30" s="637"/>
       <c r="G30" s="120"/>
       <c r="H30" s="223"/>
       <c r="I30" s="157"/>
@@ -17945,16 +17945,16 @@
       <c r="M30" s="101"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="622" t="s">
+      <c r="A31" s="618" t="s">
         <v>356</v>
       </c>
-      <c r="B31" s="623"/>
-      <c r="C31" s="611" t="s">
+      <c r="B31" s="619"/>
+      <c r="C31" s="632" t="s">
         <v>357</v>
       </c>
-      <c r="D31" s="611"/>
-      <c r="E31" s="611"/>
-      <c r="F31" s="612"/>
+      <c r="D31" s="632"/>
+      <c r="E31" s="632"/>
+      <c r="F31" s="633"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="I31" s="22"/>
@@ -17966,18 +17966,18 @@
     <row r="32" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
       <c r="B32" s="25"/>
-      <c r="C32" s="602"/>
-      <c r="D32" s="602"/>
-      <c r="E32" s="602"/>
-      <c r="F32" s="601"/>
-      <c r="G32" s="658" t="s">
+      <c r="C32" s="634"/>
+      <c r="D32" s="634"/>
+      <c r="E32" s="634"/>
+      <c r="F32" s="635"/>
+      <c r="G32" s="670" t="s">
         <v>358</v>
       </c>
-      <c r="H32" s="659"/>
-      <c r="I32" s="659"/>
-      <c r="J32" s="659"/>
-      <c r="K32" s="624"/>
-      <c r="L32" s="624"/>
+      <c r="H32" s="671"/>
+      <c r="I32" s="671"/>
+      <c r="J32" s="671"/>
+      <c r="K32" s="669"/>
+      <c r="L32" s="669"/>
       <c r="M32" s="99"/>
     </row>
     <row r="33" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17998,44 +17998,44 @@
     <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="24"/>
       <c r="B34" s="25"/>
-      <c r="C34" s="602" t="s">
+      <c r="C34" s="634" t="s">
         <v>359</v>
       </c>
-      <c r="D34" s="602"/>
-      <c r="E34" s="602"/>
-      <c r="F34" s="601"/>
+      <c r="D34" s="634"/>
+      <c r="E34" s="634"/>
+      <c r="F34" s="635"/>
       <c r="G34" s="98"/>
       <c r="H34" s="222"/>
-      <c r="I34" s="657"/>
-      <c r="J34" s="657"/>
-      <c r="K34" s="657"/>
-      <c r="L34" s="657"/>
+      <c r="I34" s="668"/>
+      <c r="J34" s="668"/>
+      <c r="K34" s="668"/>
+      <c r="L34" s="668"/>
       <c r="M34" s="99"/>
     </row>
     <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="24"/>
       <c r="B35" s="25"/>
-      <c r="C35" s="602"/>
-      <c r="D35" s="602"/>
-      <c r="E35" s="602"/>
-      <c r="F35" s="601"/>
-      <c r="G35" s="658" t="s">
+      <c r="C35" s="634"/>
+      <c r="D35" s="634"/>
+      <c r="E35" s="634"/>
+      <c r="F35" s="635"/>
+      <c r="G35" s="670" t="s">
         <v>358</v>
       </c>
-      <c r="H35" s="659"/>
-      <c r="I35" s="659"/>
-      <c r="J35" s="659"/>
-      <c r="K35" s="624"/>
-      <c r="L35" s="624"/>
+      <c r="H35" s="671"/>
+      <c r="I35" s="671"/>
+      <c r="J35" s="671"/>
+      <c r="K35" s="669"/>
+      <c r="L35" s="669"/>
       <c r="M35" s="99"/>
     </row>
     <row r="36" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="35"/>
       <c r="B36" s="36"/>
-      <c r="C36" s="613"/>
-      <c r="D36" s="613"/>
-      <c r="E36" s="613"/>
-      <c r="F36" s="614"/>
+      <c r="C36" s="636"/>
+      <c r="D36" s="636"/>
+      <c r="E36" s="636"/>
+      <c r="F36" s="637"/>
       <c r="G36" s="102"/>
       <c r="H36" s="46"/>
       <c r="I36" s="93"/>
@@ -18044,16 +18044,16 @@
       <c r="M36" s="101"/>
     </row>
     <row r="37" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="622" t="s">
+      <c r="A37" s="618" t="s">
         <v>360</v>
       </c>
-      <c r="B37" s="623"/>
-      <c r="C37" s="605" t="s">
+      <c r="B37" s="619"/>
+      <c r="C37" s="725" t="s">
         <v>361</v>
       </c>
-      <c r="D37" s="605"/>
-      <c r="E37" s="605"/>
-      <c r="F37" s="606"/>
+      <c r="D37" s="725"/>
+      <c r="E37" s="725"/>
+      <c r="F37" s="726"/>
       <c r="G37" s="22"/>
       <c r="H37" s="22"/>
       <c r="I37" s="22"/>
@@ -18065,61 +18065,61 @@
     <row r="38" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="24"/>
       <c r="B38" s="25"/>
-      <c r="C38" s="585"/>
-      <c r="D38" s="585"/>
-      <c r="E38" s="585"/>
-      <c r="F38" s="607"/>
-      <c r="G38" s="586" t="s">
+      <c r="C38" s="727"/>
+      <c r="D38" s="727"/>
+      <c r="E38" s="727"/>
+      <c r="F38" s="728"/>
+      <c r="G38" s="622" t="s">
         <v>362</v>
       </c>
-      <c r="H38" s="587"/>
-      <c r="I38" s="587"/>
-      <c r="J38" s="587"/>
-      <c r="K38" s="587"/>
-      <c r="L38" s="587"/>
-      <c r="M38" s="712"/>
+      <c r="H38" s="623"/>
+      <c r="I38" s="623"/>
+      <c r="J38" s="623"/>
+      <c r="K38" s="623"/>
+      <c r="L38" s="623"/>
+      <c r="M38" s="624"/>
     </row>
     <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="24"/>
       <c r="B39" s="25"/>
-      <c r="C39" s="585"/>
-      <c r="D39" s="585"/>
-      <c r="E39" s="585"/>
-      <c r="F39" s="607"/>
+      <c r="C39" s="727"/>
+      <c r="D39" s="727"/>
+      <c r="E39" s="727"/>
+      <c r="F39" s="728"/>
       <c r="G39" s="98"/>
       <c r="H39" s="221"/>
-      <c r="I39" s="610"/>
-      <c r="J39" s="610"/>
-      <c r="K39" s="610"/>
-      <c r="L39" s="610"/>
+      <c r="I39" s="631"/>
+      <c r="J39" s="631"/>
+      <c r="K39" s="631"/>
+      <c r="L39" s="631"/>
       <c r="M39" s="99"/>
     </row>
     <row r="40" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="35"/>
       <c r="B40" s="36"/>
-      <c r="C40" s="608"/>
-      <c r="D40" s="608"/>
-      <c r="E40" s="608"/>
-      <c r="F40" s="609"/>
+      <c r="C40" s="729"/>
+      <c r="D40" s="729"/>
+      <c r="E40" s="729"/>
+      <c r="F40" s="730"/>
       <c r="G40" s="100"/>
       <c r="H40" s="221"/>
-      <c r="I40" s="589"/>
-      <c r="J40" s="589"/>
-      <c r="K40" s="589"/>
-      <c r="L40" s="589"/>
+      <c r="I40" s="724"/>
+      <c r="J40" s="724"/>
+      <c r="K40" s="724"/>
+      <c r="L40" s="724"/>
       <c r="M40" s="101"/>
     </row>
     <row r="41" spans="1:14" ht="41.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="603" t="s">
+      <c r="A41" s="722" t="s">
         <v>363</v>
       </c>
-      <c r="B41" s="604"/>
-      <c r="C41" s="602" t="s">
+      <c r="B41" s="723"/>
+      <c r="C41" s="634" t="s">
         <v>364</v>
       </c>
-      <c r="D41" s="602"/>
-      <c r="E41" s="602"/>
-      <c r="F41" s="601"/>
+      <c r="D41" s="634"/>
+      <c r="E41" s="634"/>
+      <c r="F41" s="635"/>
       <c r="G41" s="22"/>
       <c r="H41" s="22"/>
       <c r="I41" s="41"/>
@@ -18131,10 +18131,10 @@
     <row r="42" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="39"/>
       <c r="B42" s="40"/>
-      <c r="C42" s="602"/>
-      <c r="D42" s="602"/>
-      <c r="E42" s="602"/>
-      <c r="F42" s="601"/>
+      <c r="C42" s="634"/>
+      <c r="D42" s="634"/>
+      <c r="E42" s="634"/>
+      <c r="F42" s="635"/>
       <c r="G42" s="44"/>
       <c r="H42" s="44"/>
       <c r="I42" s="44"/>
@@ -18148,21 +18148,21 @@
         <v>365</v>
       </c>
       <c r="B43" s="40"/>
-      <c r="C43" s="602" t="s">
+      <c r="C43" s="634" t="s">
         <v>366</v>
       </c>
-      <c r="D43" s="602"/>
-      <c r="E43" s="602"/>
-      <c r="F43" s="601"/>
+      <c r="D43" s="634"/>
+      <c r="E43" s="634"/>
+      <c r="F43" s="635"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="39"/>
       <c r="B44" s="40"/>
-      <c r="C44" s="602"/>
-      <c r="D44" s="602"/>
-      <c r="E44" s="602"/>
-      <c r="F44" s="601"/>
+      <c r="C44" s="634"/>
+      <c r="D44" s="634"/>
+      <c r="E44" s="634"/>
+      <c r="F44" s="635"/>
       <c r="G44" s="167" t="s">
         <v>367</v>
       </c>
@@ -18178,21 +18178,21 @@
         <v>368</v>
       </c>
       <c r="B45" s="40"/>
-      <c r="C45" s="601" t="s">
+      <c r="C45" s="635" t="s">
         <v>369</v>
       </c>
-      <c r="D45" s="601"/>
-      <c r="E45" s="601"/>
-      <c r="F45" s="601"/>
+      <c r="D45" s="635"/>
+      <c r="E45" s="635"/>
+      <c r="F45" s="635"/>
       <c r="M45" s="2"/>
     </row>
     <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="39"/>
       <c r="B46" s="40"/>
-      <c r="C46" s="601"/>
-      <c r="D46" s="601"/>
-      <c r="E46" s="601"/>
-      <c r="F46" s="601"/>
+      <c r="C46" s="635"/>
+      <c r="D46" s="635"/>
+      <c r="E46" s="635"/>
+      <c r="F46" s="635"/>
       <c r="G46" s="168" t="s">
         <v>370</v>
       </c>
@@ -18209,21 +18209,21 @@
         <v>371</v>
       </c>
       <c r="B47" s="40"/>
-      <c r="C47" s="602" t="s">
+      <c r="C47" s="634" t="s">
         <v>372</v>
       </c>
-      <c r="D47" s="602"/>
+      <c r="D47" s="634"/>
       <c r="E47" s="90"/>
       <c r="F47" s="91"/>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="637"/>
-      <c r="B48" s="638"/>
-      <c r="C48" s="638"/>
-      <c r="D48" s="638"/>
-      <c r="E48" s="638"/>
-      <c r="F48" s="639"/>
+      <c r="A48" s="685"/>
+      <c r="B48" s="686"/>
+      <c r="C48" s="686"/>
+      <c r="D48" s="686"/>
+      <c r="E48" s="686"/>
+      <c r="F48" s="687"/>
       <c r="G48" s="169" t="s">
         <v>370</v>
       </c>
@@ -18236,12 +18236,12 @@
       <c r="N48" s="46"/>
     </row>
     <row r="49" spans="1:14" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="640"/>
-      <c r="B49" s="641"/>
-      <c r="C49" s="641"/>
-      <c r="D49" s="641"/>
-      <c r="E49" s="641"/>
-      <c r="F49" s="642"/>
+      <c r="A49" s="688"/>
+      <c r="B49" s="689"/>
+      <c r="C49" s="689"/>
+      <c r="D49" s="689"/>
+      <c r="E49" s="689"/>
+      <c r="F49" s="690"/>
       <c r="G49" s="92"/>
       <c r="H49" s="88"/>
       <c r="I49" s="88"/>
@@ -18252,10 +18252,10 @@
       <c r="N49" s="46"/>
     </row>
     <row r="50" spans="1:14" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="710" t="s">
+      <c r="A50" s="620" t="s">
         <v>373</v>
       </c>
-      <c r="B50" s="711"/>
+      <c r="B50" s="621"/>
       <c r="C50" s="165" t="s">
         <v>374</v>
       </c>
@@ -18265,127 +18265,127 @@
       <c r="G50" s="165"/>
       <c r="H50" s="165"/>
       <c r="I50" s="166"/>
-      <c r="J50" s="625"/>
-      <c r="K50" s="626"/>
-      <c r="L50" s="626"/>
-      <c r="M50" s="627"/>
+      <c r="J50" s="672"/>
+      <c r="K50" s="673"/>
+      <c r="L50" s="673"/>
+      <c r="M50" s="674"/>
     </row>
     <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="634" t="s">
+      <c r="A51" s="682" t="s">
         <v>375</v>
       </c>
-      <c r="B51" s="635"/>
-      <c r="C51" s="635"/>
-      <c r="D51" s="635"/>
-      <c r="E51" s="636"/>
+      <c r="B51" s="683"/>
+      <c r="C51" s="683"/>
+      <c r="D51" s="683"/>
+      <c r="E51" s="684"/>
       <c r="F51" s="237" t="s">
         <v>376</v>
       </c>
-      <c r="G51" s="386" t="s">
+      <c r="G51" s="357" t="s">
         <v>377</v>
       </c>
-      <c r="H51" s="561"/>
-      <c r="I51" s="387"/>
-      <c r="J51" s="628"/>
-      <c r="K51" s="629"/>
-      <c r="L51" s="629"/>
-      <c r="M51" s="630"/>
+      <c r="H51" s="544"/>
+      <c r="I51" s="358"/>
+      <c r="J51" s="675"/>
+      <c r="K51" s="676"/>
+      <c r="L51" s="676"/>
+      <c r="M51" s="677"/>
     </row>
     <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="650"/>
-      <c r="B52" s="651"/>
-      <c r="C52" s="653"/>
-      <c r="D52" s="653"/>
-      <c r="E52" s="654"/>
+      <c r="A52" s="700"/>
+      <c r="B52" s="701"/>
+      <c r="C52" s="703"/>
+      <c r="D52" s="703"/>
+      <c r="E52" s="704"/>
       <c r="F52" s="47"/>
-      <c r="G52" s="643"/>
-      <c r="H52" s="644"/>
-      <c r="I52" s="645"/>
-      <c r="J52" s="628"/>
-      <c r="K52" s="629"/>
-      <c r="L52" s="629"/>
-      <c r="M52" s="630"/>
+      <c r="G52" s="693"/>
+      <c r="H52" s="694"/>
+      <c r="I52" s="695"/>
+      <c r="J52" s="675"/>
+      <c r="K52" s="676"/>
+      <c r="L52" s="676"/>
+      <c r="M52" s="677"/>
     </row>
     <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="650"/>
-      <c r="B53" s="651"/>
-      <c r="C53" s="651"/>
-      <c r="D53" s="651"/>
-      <c r="E53" s="652"/>
+      <c r="A53" s="700"/>
+      <c r="B53" s="701"/>
+      <c r="C53" s="701"/>
+      <c r="D53" s="701"/>
+      <c r="E53" s="702"/>
       <c r="F53" s="47"/>
-      <c r="G53" s="643"/>
-      <c r="H53" s="644"/>
-      <c r="I53" s="645"/>
-      <c r="J53" s="628"/>
-      <c r="K53" s="629"/>
-      <c r="L53" s="629"/>
-      <c r="M53" s="630"/>
+      <c r="G53" s="693"/>
+      <c r="H53" s="694"/>
+      <c r="I53" s="695"/>
+      <c r="J53" s="675"/>
+      <c r="K53" s="676"/>
+      <c r="L53" s="676"/>
+      <c r="M53" s="677"/>
     </row>
     <row r="54" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="646"/>
-      <c r="B54" s="647"/>
-      <c r="C54" s="648"/>
-      <c r="D54" s="648"/>
-      <c r="E54" s="649"/>
+      <c r="A54" s="696"/>
+      <c r="B54" s="697"/>
+      <c r="C54" s="698"/>
+      <c r="D54" s="698"/>
+      <c r="E54" s="699"/>
       <c r="F54" s="174"/>
-      <c r="G54" s="631"/>
-      <c r="H54" s="632"/>
-      <c r="I54" s="633"/>
-      <c r="J54" s="628"/>
-      <c r="K54" s="629"/>
-      <c r="L54" s="629"/>
-      <c r="M54" s="630"/>
+      <c r="G54" s="679"/>
+      <c r="H54" s="680"/>
+      <c r="I54" s="681"/>
+      <c r="J54" s="675"/>
+      <c r="K54" s="676"/>
+      <c r="L54" s="676"/>
+      <c r="M54" s="677"/>
     </row>
     <row r="55" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="615" t="s">
+      <c r="A55" s="691" t="s">
         <v>378</v>
       </c>
-      <c r="B55" s="616"/>
-      <c r="C55" s="655" t="s">
+      <c r="B55" s="692"/>
+      <c r="C55" s="705" t="s">
         <v>399</v>
       </c>
-      <c r="D55" s="655"/>
-      <c r="E55" s="655"/>
-      <c r="F55" s="655"/>
-      <c r="G55" s="655"/>
-      <c r="H55" s="655"/>
+      <c r="D55" s="705"/>
+      <c r="E55" s="705"/>
+      <c r="F55" s="705"/>
+      <c r="G55" s="705"/>
+      <c r="H55" s="705"/>
       <c r="I55" s="227"/>
-      <c r="J55" s="629"/>
-      <c r="K55" s="629"/>
-      <c r="L55" s="629"/>
-      <c r="M55" s="630"/>
+      <c r="J55" s="676"/>
+      <c r="K55" s="676"/>
+      <c r="L55" s="676"/>
+      <c r="M55" s="677"/>
     </row>
     <row r="56" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="48"/>
       <c r="B56" s="49"/>
-      <c r="C56" s="656"/>
-      <c r="D56" s="656"/>
-      <c r="E56" s="656"/>
-      <c r="F56" s="656"/>
-      <c r="G56" s="656"/>
-      <c r="H56" s="656"/>
+      <c r="C56" s="706"/>
+      <c r="D56" s="706"/>
+      <c r="E56" s="706"/>
+      <c r="F56" s="706"/>
+      <c r="G56" s="706"/>
+      <c r="H56" s="706"/>
       <c r="I56" s="228"/>
       <c r="J56" s="173"/>
-      <c r="K56" s="597" t="s">
+      <c r="K56" s="678" t="s">
         <v>379</v>
       </c>
-      <c r="L56" s="597"/>
+      <c r="L56" s="678"/>
       <c r="M56" s="156"/>
     </row>
     <row r="57" spans="1:14" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="48"/>
       <c r="B57" s="49"/>
-      <c r="C57" s="656"/>
-      <c r="D57" s="656"/>
-      <c r="E57" s="656"/>
-      <c r="F57" s="656"/>
-      <c r="G57" s="656"/>
-      <c r="H57" s="656"/>
+      <c r="C57" s="706"/>
+      <c r="D57" s="706"/>
+      <c r="E57" s="706"/>
+      <c r="F57" s="706"/>
+      <c r="G57" s="706"/>
+      <c r="H57" s="706"/>
       <c r="I57" s="228"/>
-      <c r="J57" s="597"/>
-      <c r="K57" s="597"/>
-      <c r="L57" s="597"/>
-      <c r="M57" s="598"/>
+      <c r="J57" s="678"/>
+      <c r="K57" s="678"/>
+      <c r="L57" s="678"/>
+      <c r="M57" s="721"/>
     </row>
     <row r="58" spans="1:14" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="154"/>
@@ -18397,8 +18397,8 @@
       <c r="G58" s="229"/>
       <c r="H58" s="229"/>
       <c r="I58" s="230"/>
-      <c r="K58" s="681"/>
-      <c r="L58" s="682"/>
+      <c r="K58" s="658"/>
+      <c r="L58" s="659"/>
       <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:14" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18410,104 +18410,104 @@
       <c r="G59" s="17"/>
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
-      <c r="K59" s="683"/>
-      <c r="L59" s="684"/>
+      <c r="K59" s="660"/>
+      <c r="L59" s="661"/>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:14" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="50"/>
-      <c r="B60" s="703" t="s">
+      <c r="B60" s="610" t="s">
         <v>400</v>
       </c>
-      <c r="C60" s="704"/>
-      <c r="D60" s="705"/>
-      <c r="F60" s="694" t="s">
+      <c r="C60" s="611"/>
+      <c r="D60" s="612"/>
+      <c r="F60" s="601" t="s">
         <v>144</v>
       </c>
-      <c r="G60" s="695"/>
-      <c r="H60" s="695"/>
-      <c r="I60" s="696"/>
-      <c r="K60" s="683"/>
-      <c r="L60" s="684"/>
+      <c r="G60" s="602"/>
+      <c r="H60" s="602"/>
+      <c r="I60" s="603"/>
+      <c r="K60" s="660"/>
+      <c r="L60" s="661"/>
       <c r="M60" s="51"/>
     </row>
     <row r="61" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="50"/>
-      <c r="B61" s="687" t="s">
+      <c r="B61" s="664" t="s">
         <v>380</v>
       </c>
-      <c r="C61" s="688"/>
+      <c r="C61" s="665"/>
       <c r="D61" s="107"/>
-      <c r="F61" s="697"/>
-      <c r="G61" s="698"/>
-      <c r="H61" s="698"/>
-      <c r="I61" s="699"/>
-      <c r="K61" s="683"/>
-      <c r="L61" s="684"/>
+      <c r="F61" s="604"/>
+      <c r="G61" s="605"/>
+      <c r="H61" s="605"/>
+      <c r="I61" s="606"/>
+      <c r="K61" s="660"/>
+      <c r="L61" s="661"/>
       <c r="M61" s="51"/>
     </row>
     <row r="62" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="50"/>
-      <c r="B62" s="675" t="s">
+      <c r="B62" s="653" t="s">
         <v>381</v>
       </c>
-      <c r="C62" s="676"/>
-      <c r="D62" s="679"/>
-      <c r="F62" s="700"/>
-      <c r="G62" s="701"/>
-      <c r="H62" s="701"/>
-      <c r="I62" s="702"/>
-      <c r="K62" s="683"/>
-      <c r="L62" s="684"/>
+      <c r="C62" s="654"/>
+      <c r="D62" s="613"/>
+      <c r="F62" s="607"/>
+      <c r="G62" s="608"/>
+      <c r="H62" s="608"/>
+      <c r="I62" s="609"/>
+      <c r="K62" s="660"/>
+      <c r="L62" s="661"/>
       <c r="M62" s="51"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="50"/>
-      <c r="B63" s="689"/>
-      <c r="C63" s="690"/>
-      <c r="D63" s="706"/>
-      <c r="F63" s="707" t="s">
+      <c r="B63" s="666"/>
+      <c r="C63" s="667"/>
+      <c r="D63" s="614"/>
+      <c r="F63" s="615" t="s">
         <v>382</v>
       </c>
-      <c r="G63" s="708"/>
-      <c r="H63" s="708"/>
-      <c r="I63" s="709"/>
-      <c r="K63" s="683"/>
-      <c r="L63" s="684"/>
+      <c r="G63" s="616"/>
+      <c r="H63" s="616"/>
+      <c r="I63" s="617"/>
+      <c r="K63" s="660"/>
+      <c r="L63" s="661"/>
       <c r="M63" s="51"/>
     </row>
     <row r="64" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="50"/>
-      <c r="B64" s="675" t="s">
+      <c r="B64" s="653" t="s">
         <v>383</v>
       </c>
-      <c r="C64" s="676"/>
-      <c r="D64" s="679"/>
+      <c r="C64" s="654"/>
+      <c r="D64" s="613"/>
       <c r="F64" s="52"/>
       <c r="G64" s="157"/>
       <c r="H64" s="157"/>
       <c r="I64" s="158"/>
       <c r="J64" s="53"/>
-      <c r="K64" s="685"/>
-      <c r="L64" s="686"/>
+      <c r="K64" s="662"/>
+      <c r="L64" s="663"/>
       <c r="M64" s="51"/>
     </row>
     <row r="65" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="50"/>
-      <c r="B65" s="677"/>
-      <c r="C65" s="678"/>
-      <c r="D65" s="680"/>
-      <c r="F65" s="672" t="s">
+      <c r="B65" s="655"/>
+      <c r="C65" s="656"/>
+      <c r="D65" s="657"/>
+      <c r="F65" s="650" t="s">
         <v>384</v>
       </c>
-      <c r="G65" s="673"/>
-      <c r="H65" s="673"/>
-      <c r="I65" s="674"/>
+      <c r="G65" s="651"/>
+      <c r="H65" s="651"/>
+      <c r="I65" s="652"/>
       <c r="J65" s="53"/>
-      <c r="K65" s="670" t="s">
+      <c r="K65" s="648" t="s">
         <v>385</v>
       </c>
-      <c r="L65" s="671"/>
+      <c r="L65" s="649"/>
       <c r="M65" s="51"/>
     </row>
     <row r="66" spans="1:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18526,34 +18526,34 @@
       <c r="M66" s="59"/>
     </row>
     <row r="67" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="667" t="s">
+      <c r="A67" s="645" t="s">
         <v>386</v>
       </c>
-      <c r="B67" s="668"/>
-      <c r="C67" s="668"/>
-      <c r="D67" s="668"/>
-      <c r="E67" s="668"/>
-      <c r="F67" s="668"/>
-      <c r="G67" s="668"/>
-      <c r="H67" s="668"/>
-      <c r="I67" s="668"/>
-      <c r="J67" s="668"/>
-      <c r="K67" s="668"/>
-      <c r="L67" s="668"/>
-      <c r="M67" s="669"/>
+      <c r="B67" s="646"/>
+      <c r="C67" s="646"/>
+      <c r="D67" s="646"/>
+      <c r="E67" s="646"/>
+      <c r="F67" s="646"/>
+      <c r="G67" s="646"/>
+      <c r="H67" s="646"/>
+      <c r="I67" s="646"/>
+      <c r="J67" s="646"/>
+      <c r="K67" s="646"/>
+      <c r="L67" s="646"/>
+      <c r="M67" s="647"/>
     </row>
     <row r="68" spans="1:13" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="50"/>
       <c r="B68" s="53"/>
       <c r="C68" s="60"/>
       <c r="D68" s="60"/>
-      <c r="E68" s="664" t="s">
+      <c r="E68" s="642" t="s">
         <v>387</v>
       </c>
-      <c r="F68" s="665"/>
-      <c r="G68" s="665"/>
-      <c r="H68" s="665"/>
-      <c r="I68" s="666"/>
+      <c r="F68" s="643"/>
+      <c r="G68" s="643"/>
+      <c r="H68" s="643"/>
+      <c r="I68" s="644"/>
       <c r="J68" s="108"/>
       <c r="K68" s="108"/>
       <c r="M68" s="51"/>
@@ -18563,13 +18563,13 @@
       <c r="B69" s="53"/>
       <c r="C69" s="212"/>
       <c r="D69" s="212"/>
-      <c r="E69" s="661" t="s">
+      <c r="E69" s="639" t="s">
         <v>388</v>
       </c>
-      <c r="F69" s="662"/>
-      <c r="G69" s="662"/>
-      <c r="H69" s="662"/>
-      <c r="I69" s="663"/>
+      <c r="F69" s="640"/>
+      <c r="G69" s="640"/>
+      <c r="H69" s="640"/>
+      <c r="I69" s="641"/>
       <c r="J69" s="110"/>
       <c r="K69" s="109"/>
       <c r="L69" s="61"/>
@@ -18591,21 +18591,21 @@
       <c r="M70" s="64"/>
     </row>
     <row r="71" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="660" t="s">
+      <c r="A71" s="638" t="s">
         <v>402</v>
       </c>
-      <c r="B71" s="660"/>
-      <c r="C71" s="660"/>
-      <c r="D71" s="660"/>
-      <c r="E71" s="660"/>
-      <c r="F71" s="660"/>
-      <c r="G71" s="660"/>
-      <c r="H71" s="660"/>
-      <c r="I71" s="660"/>
-      <c r="J71" s="660"/>
-      <c r="K71" s="660"/>
-      <c r="L71" s="660"/>
-      <c r="M71" s="660"/>
+      <c r="B71" s="638"/>
+      <c r="C71" s="638"/>
+      <c r="D71" s="638"/>
+      <c r="E71" s="638"/>
+      <c r="F71" s="638"/>
+      <c r="G71" s="638"/>
+      <c r="H71" s="638"/>
+      <c r="I71" s="638"/>
+      <c r="J71" s="638"/>
+      <c r="K71" s="638"/>
+      <c r="L71" s="638"/>
+      <c r="M71" s="638"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -18618,6 +18618,75 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="85">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F16"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C45:F46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="C37:F40"/>
+    <mergeCell ref="C41:F42"/>
+    <mergeCell ref="C43:F44"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="C27:F30"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="J50:M55"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A48:F49"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="C55:H57"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="C31:F32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C34:F36"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="A71:M71"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="A67:M67"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="B64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="K58:L64"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C63"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="F60:I62"/>
@@ -18634,75 +18703,6 @@
     <mergeCell ref="G19:L19"/>
     <mergeCell ref="I25:L25"/>
     <mergeCell ref="C23:F26"/>
-    <mergeCell ref="A71:M71"/>
-    <mergeCell ref="E69:I69"/>
-    <mergeCell ref="E68:I68"/>
-    <mergeCell ref="A67:M67"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="B64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="K58:L64"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C63"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C31:F32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C34:F36"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="J50:M55"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A48:F49"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="C55:H57"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C45:F46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="C37:F40"/>
-    <mergeCell ref="C41:F42"/>
-    <mergeCell ref="C43:F44"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="C27:F30"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F16"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -19339,6 +19339,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004061E9AFAF7CA04B82F43B8373745610" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3807037a0979b6ce9196f65959799221">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="61535973-5223-4bf4-bdcc-6c7df9166676" xmlns:ns3="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0698124c94b6a25b909cbe33b647c32f" ns2:_="" ns3:_="">
     <xsd:import namespace="61535973-5223-4bf4-bdcc-6c7df9166676"/>
@@ -19569,15 +19578,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -19589,6 +19589,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99101B7C-E13F-4ECC-92B9-66DA7C9E1E4F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19603,14 +19611,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
